--- a/isgon.xlsx
+++ b/isgon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CB8938-8FA0-41D7-825F-6A207B30AFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A370460C-F2DE-4CA3-8584-34A1770C6634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{AE089D8B-92F7-455A-B330-531FF778F1FC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4932" uniqueCount="3373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4996" uniqueCount="3437">
   <si>
     <t>CODIGO</t>
   </si>
@@ -10157,7 +10157,199 @@
     <t>https://promart.vteximg.com.br/arquivos/ids/7595249-1000-1000/imageUrl_1.jpg</t>
   </si>
   <si>
-    <t>https://cdnx.jumpseller.com/tecnohard/image/51497171/ASUS_A31N1601-min.jpg</t>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/08/0301097-BATERIA-AS-A31N1601-36Wh-10.8V-3-CELDAS-X541-X541U-INT.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/85_0304368_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/09/282_0304997_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/S224a84977c90444586dd0471f0f6d57dA.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/02/160_0304593_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/89_0304426_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/05/215_0304585_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/11/312_0301143_FONBLAN-3.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/219_0304642_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/64_0304457_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/191_0304846_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/02/236_0304953_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/5_0301019_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/11_0302089_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61AJeqeGhkL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/Sbd5088b801cb4e13ad0f23eb804955ddQ.jpg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/128163870_01/public?wid=200&amp;hei=200&amp;qlt=70&amp;fmt=webp</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/S4d34ec5d7b604759b4612dcfc2c93ea1E.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51yqLDLdzIL.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0304430_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/DELL-33YDH-56Wh-15.2V-4-CELDAS-SIN-LOGO.png</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/21_0304450_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_860523-MPE92314155578_092025-O.webp</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/193_0304840_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/05/166_0304366_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2025/08/373_0308099_FONBALN.png</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/05/110_0304419_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61hJH7qvXyL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/11/135_0304518_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_874982-MPE83022382338_032025-O.webp</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/41KgHdG2hrL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61nzmVAKLfL.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/810iB7P6ZnL.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/1_0301005_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/2_0301025_FONBLAN-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/13_0301008_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/26_0301066_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/11/100_0301061_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://sc04.alicdn.com/kf/H080770ad6f0a4326afd43ca63e702456a.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/76_0301068_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_794904-MPE79858203411_102024-O.webp</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/38_0301010_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/Sba823fad11e4419aa4a169a94210eb13P.png</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0301007_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/08/0301012-BATERIA-H-HSTNN-LB2H-CC06-55Wh-10.8V-6-CELDAS-6360B-6460B-6465B-6560B-6570B-8460P-EXT-scaled.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0301087_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61mC+M6EA+L._AC_UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71EzXYFRBfL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/230_0304373_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0301016_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/6_0302091_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81pVBC9+xxL.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81jI+5LVLKL.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0304378_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/61_0304365_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/S89c3778ee9f04bff862260b90c6696db5.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/616CnoKgnEL.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/69_0304360_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71VoTt8nA6L.jpg_BO30,255,255,255_UF750,750_SR1910,1000,0,C_QL100_.jpg</t>
+  </si>
+  <si>
+    <t>https://rimage.ripley.com.pe/home.ripley/Attachment/MKP/5576/PMP20000770253/full_image-1.jpeg</t>
+  </si>
+  <si>
+    <t>https://sc04.alicdn.com/kf/Hb7e6962fb15749f69893fc88ad8ae244T.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/05/136_0304524_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0304402_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61QKhJaGa9S.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/05/179_0304564_FONBLAN.jpg</t>
   </si>
 </sst>
 </file>
@@ -12715,7 +12907,9 @@
       <c r="C112" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D112" s="4"/>
+      <c r="D112" s="4" t="s">
+        <v>3373</v>
+      </c>
       <c r="E112" s="3">
         <v>90</v>
       </c>
@@ -12736,7 +12930,9 @@
       <c r="C113" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D113" s="4"/>
+      <c r="D113" s="4" t="s">
+        <v>3374</v>
+      </c>
       <c r="E113" s="3">
         <v>80</v>
       </c>
@@ -12802,7 +12998,9 @@
       <c r="C117" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D117" s="4"/>
+      <c r="D117" s="4" t="s">
+        <v>3375</v>
+      </c>
       <c r="E117" s="3">
         <v>100</v>
       </c>
@@ -12838,7 +13036,9 @@
       <c r="C119" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D119" s="4"/>
+      <c r="D119" s="4" t="s">
+        <v>3376</v>
+      </c>
       <c r="E119" s="3">
         <v>90</v>
       </c>
@@ -12889,7 +13089,9 @@
       <c r="C122" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D122" s="4"/>
+      <c r="D122" s="4" t="s">
+        <v>3377</v>
+      </c>
       <c r="E122" s="3">
         <v>120</v>
       </c>
@@ -12936,7 +13138,9 @@
       <c r="C125" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D125" s="4"/>
+      <c r="D125" s="4" t="s">
+        <v>3378</v>
+      </c>
       <c r="E125" s="3">
         <v>100</v>
       </c>
@@ -12957,7 +13161,9 @@
       <c r="C126" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D126" s="4"/>
+      <c r="D126" s="4" t="s">
+        <v>3379</v>
+      </c>
       <c r="E126" s="3">
         <v>80</v>
       </c>
@@ -13008,7 +13214,9 @@
       <c r="C129" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D129" s="4"/>
+      <c r="D129" s="4" t="s">
+        <v>3380</v>
+      </c>
       <c r="E129" s="3">
         <v>95</v>
       </c>
@@ -13059,7 +13267,9 @@
       <c r="C132" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D132" s="4"/>
+      <c r="D132" s="4" t="s">
+        <v>3381</v>
+      </c>
       <c r="E132" s="3">
         <v>65</v>
       </c>
@@ -13181,7 +13391,9 @@
       <c r="C140" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D140" s="4"/>
+      <c r="D140" s="4" t="s">
+        <v>3382</v>
+      </c>
       <c r="E140" s="3">
         <v>115</v>
       </c>
@@ -13232,7 +13444,9 @@
       <c r="C143" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D143" s="4"/>
+      <c r="D143" s="4" t="s">
+        <v>3383</v>
+      </c>
       <c r="E143" s="3">
         <v>110</v>
       </c>
@@ -13508,7 +13722,9 @@
       <c r="C161" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D161" s="4"/>
+      <c r="D161" s="4" t="s">
+        <v>3384</v>
+      </c>
       <c r="E161" s="3">
         <v>65</v>
       </c>
@@ -13550,7 +13766,9 @@
       <c r="C163" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D163" s="4"/>
+      <c r="D163" s="4" t="s">
+        <v>3385</v>
+      </c>
       <c r="E163" s="3">
         <v>100</v>
       </c>
@@ -13601,7 +13819,9 @@
       <c r="C166" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D166" s="4"/>
+      <c r="D166" s="4" t="s">
+        <v>3386</v>
+      </c>
       <c r="E166" s="3">
         <v>70</v>
       </c>
@@ -13633,7 +13853,9 @@
       <c r="C168" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D168" s="4"/>
+      <c r="D168" s="4" t="s">
+        <v>3387</v>
+      </c>
       <c r="E168" s="3">
         <v>130</v>
       </c>
@@ -13669,7 +13891,9 @@
       <c r="C170" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D170" s="4"/>
+      <c r="D170" s="4" t="s">
+        <v>3389</v>
+      </c>
       <c r="E170" s="3">
         <v>90</v>
       </c>
@@ -13690,7 +13914,9 @@
       <c r="C171" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D171" s="4"/>
+      <c r="D171" s="4" t="s">
+        <v>3390</v>
+      </c>
       <c r="E171" s="3">
         <v>115</v>
       </c>
@@ -13711,7 +13937,9 @@
       <c r="C172" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D172" s="4"/>
+      <c r="D172" s="4" t="s">
+        <v>3391</v>
+      </c>
       <c r="E172" s="3">
         <v>100</v>
       </c>
@@ -13732,7 +13960,9 @@
       <c r="C173" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D173" s="4"/>
+      <c r="D173" s="4" t="s">
+        <v>3388</v>
+      </c>
       <c r="E173" s="3">
         <v>95</v>
       </c>
@@ -13753,7 +13983,9 @@
       <c r="C174" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D174" s="4"/>
+      <c r="D174" s="4" t="s">
+        <v>3392</v>
+      </c>
       <c r="E174" s="3">
         <v>95</v>
       </c>
@@ -13774,7 +14006,9 @@
       <c r="C175" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D175" s="4"/>
+      <c r="D175" s="4" t="s">
+        <v>3393</v>
+      </c>
       <c r="E175" s="3">
         <v>95</v>
       </c>
@@ -13870,7 +14104,9 @@
       <c r="C181" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D181" s="4"/>
+      <c r="D181" s="4" t="s">
+        <v>3394</v>
+      </c>
       <c r="E181" s="3">
         <v>115</v>
       </c>
@@ -13906,7 +14142,9 @@
       <c r="C183" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D183" s="4"/>
+      <c r="D183" s="4" t="s">
+        <v>3395</v>
+      </c>
       <c r="E183" s="3">
         <v>110</v>
       </c>
@@ -13957,7 +14195,9 @@
       <c r="C186" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D186" s="4"/>
+      <c r="D186" s="4" t="s">
+        <v>3396</v>
+      </c>
       <c r="E186" s="3">
         <v>95</v>
       </c>
@@ -14014,7 +14254,9 @@
       <c r="C189" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D189" s="4"/>
+      <c r="D189" s="4" t="s">
+        <v>3397</v>
+      </c>
       <c r="E189" s="3">
         <v>105</v>
       </c>
@@ -14035,7 +14277,9 @@
       <c r="C190" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D190" s="4"/>
+      <c r="D190" s="4" t="s">
+        <v>3398</v>
+      </c>
       <c r="E190" s="3">
         <v>95</v>
       </c>
@@ -14161,7 +14405,9 @@
       <c r="C198" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D198" s="4"/>
+      <c r="D198" s="4" t="s">
+        <v>3399</v>
+      </c>
       <c r="E198" s="3">
         <v>100</v>
       </c>
@@ -14197,7 +14443,9 @@
       <c r="C200" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D200" s="4"/>
+      <c r="D200" s="4" t="s">
+        <v>3400</v>
+      </c>
       <c r="E200" s="3">
         <v>85</v>
       </c>
@@ -14351,7 +14599,9 @@
       <c r="C210" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D210" s="4"/>
+      <c r="D210" s="4" t="s">
+        <v>3401</v>
+      </c>
       <c r="E210" s="3">
         <v>60</v>
       </c>
@@ -14372,7 +14622,9 @@
       <c r="C211" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D211" s="4"/>
+      <c r="D211" s="4" t="s">
+        <v>3402</v>
+      </c>
       <c r="E211" s="3">
         <v>65</v>
       </c>
@@ -14393,7 +14645,9 @@
       <c r="C212" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D212" s="4"/>
+      <c r="D212" s="4" t="s">
+        <v>3403</v>
+      </c>
       <c r="E212" s="3">
         <v>60</v>
       </c>
@@ -14414,7 +14668,9 @@
       <c r="C213" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D213" s="4"/>
+      <c r="D213" s="4" t="s">
+        <v>3404</v>
+      </c>
       <c r="E213" s="3">
         <v>60</v>
       </c>
@@ -14435,7 +14691,9 @@
       <c r="C214" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D214" s="4"/>
+      <c r="D214" s="4" t="s">
+        <v>3405</v>
+      </c>
       <c r="E214" s="3">
         <v>60</v>
       </c>
@@ -14456,7 +14714,9 @@
       <c r="C215" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D215" s="4"/>
+      <c r="D215" s="4" t="s">
+        <v>3406</v>
+      </c>
       <c r="E215" s="3">
         <v>60</v>
       </c>
@@ -14477,7 +14737,9 @@
       <c r="C216" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D216" s="4"/>
+      <c r="D216" s="4" t="s">
+        <v>3407</v>
+      </c>
       <c r="E216" s="3">
         <v>60</v>
       </c>
@@ -14498,7 +14760,9 @@
       <c r="C217" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D217" s="4"/>
+      <c r="D217" s="4" t="s">
+        <v>3408</v>
+      </c>
       <c r="E217" s="3">
         <v>70</v>
       </c>
@@ -14519,7 +14783,9 @@
       <c r="C218" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D218" s="4"/>
+      <c r="D218" s="4" t="s">
+        <v>3409</v>
+      </c>
       <c r="E218" s="3">
         <v>70</v>
       </c>
@@ -14540,7 +14806,9 @@
       <c r="C219" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D219" s="4"/>
+      <c r="D219" s="4" t="s">
+        <v>3410</v>
+      </c>
       <c r="E219" s="3">
         <v>60</v>
       </c>
@@ -14561,7 +14829,9 @@
       <c r="C220" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D220" s="4"/>
+      <c r="D220" s="4" t="s">
+        <v>3411</v>
+      </c>
       <c r="E220" s="3">
         <v>65</v>
       </c>
@@ -14582,7 +14852,9 @@
       <c r="C221" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D221" s="4"/>
+      <c r="D221" s="4" t="s">
+        <v>3412</v>
+      </c>
       <c r="E221" s="3">
         <v>65</v>
       </c>
@@ -14603,7 +14875,9 @@
       <c r="C222" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D222" s="4"/>
+      <c r="D222" s="4" t="s">
+        <v>3413</v>
+      </c>
       <c r="E222" s="3">
         <v>65</v>
       </c>
@@ -14729,7 +15003,9 @@
       <c r="C230" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D230" s="4"/>
+      <c r="D230" s="4" t="s">
+        <v>3414</v>
+      </c>
       <c r="E230" s="3">
         <v>80</v>
       </c>
@@ -14750,7 +15026,9 @@
       <c r="C231" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D231" s="4"/>
+      <c r="D231" s="4" t="s">
+        <v>3415</v>
+      </c>
       <c r="E231" s="3">
         <v>75</v>
       </c>
@@ -14771,7 +15049,9 @@
       <c r="C232" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D232" s="4"/>
+      <c r="D232" s="4" t="s">
+        <v>3416</v>
+      </c>
       <c r="E232" s="3">
         <v>65</v>
       </c>
@@ -14828,7 +15108,9 @@
       <c r="C235" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D235" s="4"/>
+      <c r="D235" s="4" t="s">
+        <v>3417</v>
+      </c>
       <c r="E235" s="3">
         <v>65</v>
       </c>
@@ -14864,7 +15146,9 @@
       <c r="C237" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D237" s="4"/>
+      <c r="D237" s="4" t="s">
+        <v>3418</v>
+      </c>
       <c r="E237" s="3">
         <v>65</v>
       </c>
@@ -14885,7 +15169,9 @@
       <c r="C238" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D238" s="4"/>
+      <c r="D238" s="4" t="s">
+        <v>3419</v>
+      </c>
       <c r="E238" s="3">
         <v>65</v>
       </c>
@@ -14923,7 +15209,9 @@
       <c r="C240" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D240" s="4"/>
+      <c r="D240" s="4" t="s">
+        <v>3420</v>
+      </c>
       <c r="E240" s="3">
         <v>75</v>
       </c>
@@ -14944,7 +15232,9 @@
       <c r="C241" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D241" s="4"/>
+      <c r="D241" s="4" t="s">
+        <v>3421</v>
+      </c>
       <c r="E241" s="3">
         <v>65</v>
       </c>
@@ -14965,7 +15255,9 @@
       <c r="C242" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D242" s="4"/>
+      <c r="D242" s="4" t="s">
+        <v>3422</v>
+      </c>
       <c r="E242" s="3">
         <v>85</v>
       </c>
@@ -14986,7 +15278,9 @@
       <c r="C243" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D243" s="4"/>
+      <c r="D243" s="4" t="s">
+        <v>3423</v>
+      </c>
       <c r="E243" s="3">
         <v>85</v>
       </c>
@@ -15022,7 +15316,9 @@
       <c r="C245" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D245" s="4"/>
+      <c r="D245" s="4" t="s">
+        <v>3424</v>
+      </c>
       <c r="E245" s="3">
         <v>95</v>
       </c>
@@ -15043,7 +15339,9 @@
       <c r="C246" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D246" s="4"/>
+      <c r="D246" s="4" t="s">
+        <v>3425</v>
+      </c>
       <c r="E246" s="3">
         <v>90</v>
       </c>
@@ -15064,7 +15362,9 @@
       <c r="C247" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D247" s="4"/>
+      <c r="D247" s="4" t="s">
+        <v>3426</v>
+      </c>
       <c r="E247" s="3">
         <v>90</v>
       </c>
@@ -15085,7 +15385,9 @@
       <c r="C248" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D248" s="4"/>
+      <c r="D248" s="4" t="s">
+        <v>3427</v>
+      </c>
       <c r="E248" s="3">
         <v>90</v>
       </c>
@@ -15121,7 +15423,9 @@
       <c r="C250" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D250" s="4"/>
+      <c r="D250" s="4" t="s">
+        <v>3428</v>
+      </c>
       <c r="E250" s="3">
         <v>120</v>
       </c>
@@ -15138,7 +15442,9 @@
       <c r="C251" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D251" s="4"/>
+      <c r="D251" s="4" t="s">
+        <v>3429</v>
+      </c>
       <c r="E251" s="3">
         <v>70</v>
       </c>
@@ -15174,7 +15480,9 @@
       <c r="C253" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D253" s="4"/>
+      <c r="D253" s="4" t="s">
+        <v>3430</v>
+      </c>
       <c r="E253" s="3">
         <v>90</v>
       </c>
@@ -15225,7 +15533,9 @@
       <c r="C256" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D256" s="4"/>
+      <c r="D256" s="4" t="s">
+        <v>3431</v>
+      </c>
       <c r="E256" s="3">
         <v>85</v>
       </c>
@@ -15246,7 +15556,9 @@
       <c r="C257" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D257" s="4"/>
+      <c r="D257" s="4" t="s">
+        <v>3432</v>
+      </c>
       <c r="E257" s="3">
         <v>90</v>
       </c>
@@ -15402,7 +15714,9 @@
       <c r="C267" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D267" s="4"/>
+      <c r="D267" s="4" t="s">
+        <v>3433</v>
+      </c>
       <c r="E267" s="3">
         <v>95</v>
       </c>
@@ -15423,7 +15737,9 @@
       <c r="C268" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D268" s="4"/>
+      <c r="D268" s="4" t="s">
+        <v>3434</v>
+      </c>
       <c r="E268" s="3">
         <v>90</v>
       </c>
@@ -15444,7 +15760,9 @@
       <c r="C269" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D269" s="4"/>
+      <c r="D269" s="4" t="s">
+        <v>3435</v>
+      </c>
       <c r="E269" s="3">
         <v>80</v>
       </c>
@@ -15465,7 +15783,9 @@
       <c r="C270" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D270" s="4"/>
+      <c r="D270" s="4" t="s">
+        <v>3436</v>
+      </c>
       <c r="E270" s="3">
         <v>100</v>
       </c>

--- a/isgon.xlsx
+++ b/isgon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A370460C-F2DE-4CA3-8584-34A1770C6634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71375BDE-1D9F-4187-BA91-31FCBB62959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{AE089D8B-92F7-455A-B330-531FF778F1FC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4996" uniqueCount="3437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5125" uniqueCount="3564">
   <si>
     <t>CODIGO</t>
   </si>
@@ -10350,6 +10350,387 @@
   </si>
   <si>
     <t>https://cahuana.com.pe/wp-content/uploads/2024/05/179_0304564_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/02/107_0304491_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61y3gkZJ+5L._AC_UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81MxO9azVAL._AC_UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/02/254_0301105_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/02/104_0302102_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61++xwc8x7L.jpg_BO30,255,255,255_UF750,750_SR1910,1000,0,C_QL100_.jpg</t>
+  </si>
+  <si>
+    <t>https://i.ebayimg.com/images/g/yM4AAOSwSyZns98z/s-l1200.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/710kO5NXIKL._AC_UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/20_0301017_FONBLAN-scaled.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/0301031-BATERIA-LE-L11S6F01-L11N6R01-49Wh-11.1V-6-CELDAS-E530-G480-Y480-Y580-Z480-EXT.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/12_0301035_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/08/0301069-BATERIA-LE-L13L4A01-32Wh-14.4V-4-CELDAS-45N1186-M4400-B50-70-B40-70-G550S-EXT.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61yndFJnvzL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_602798-MPE92310202206_092025-O.webp</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/11/56_0304448_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/711CB9wqaML.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/16_0302094_FONBLAN.png</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/11/319_0308046_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_955097-MPE89683289136_082025-O.webp</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/93_0304405_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://s.alicdn.com/@sc04/kf/Hd6ce3c28051a4ed9ae697b1218ed8799x/Y400-Y490-Rechargeable-Li-polymer-Laptop-Battery-10.8V-for-Y490N-Y590N-Y490P-Y510A-TFI-Y400N-Y500N-Y510A-UT-Y400N-ISE.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/02030040_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71jwPYVd0jL.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/11/317_0301084_FONBLAN-3.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0301117_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0304354_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/05/146_0304542_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/02/126_0304433_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/415ZPOLL2DL._AC_UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/52_0302105_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81u9tTfeUXL.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/02/139_0304531_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/02/186_0301180_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61MI87cobqL.jpg_BO30,255,255,255_UF750,750_SR1910,1000,0,C_QL100_.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/05/111_0304451_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/03/232_0304927_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/03/245_0304961_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/03/238_0304955_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/S18ccb78d17a1435b975d1022424f810bY.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0301032_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_840056-MPE87029590726_072025-O.webp</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61HpKpa6T2L._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/S352c2a1419c043fb9b03907a150b9548U.png</t>
+  </si>
+  <si>
+    <t>https://www.computerbolt.com/cdn/shop/products/PA3534GEN.jpg</t>
+  </si>
+  <si>
+    <t>https://www.computerbolt.com/cdn/shop/products/PA3817GEN.jpg</t>
+  </si>
+  <si>
+    <t>https://www.computerbolt.com/cdn/shop/products/L800.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/0301011.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/71_0301083_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/0301024.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_Q_NP_2X_902868-MLA80152079051_102024-W.webp</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/1848095/10068883.jpg</t>
+  </si>
+  <si>
+    <t>https://pcmartcolombia.com/storage/2021/02/USB31.png</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/myfimport.com/wp-content/uploads/2020/11/cableusb3.0machomacho1.5m.jpg</t>
+  </si>
+  <si>
+    <t>https://daphtech.com/wp-content/uploads/2022/03/CABLE-EXTENSION-USB-1.5-MT-M-H-PVC_daphtech_1.jpg</t>
+  </si>
+  <si>
+    <t>https://www.compucentro.pe/wp-content/uploads/2022/04/cable-vga-1.8m.png</t>
+  </si>
+  <si>
+    <t>https://www.dealsplant.com/cdn/shop/products/dealsplant-cables-dealsplant-premium-male-to-male-vga-cable-3-meter-3m-28497332535371_1024x.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/5631576-1000-1000/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://feniximportperu.com/wp-content/uploads/2024/08/01-1-1.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/1847557/10068819.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/5631515-1000-1000/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>romart.vteximg.com.br/arquivos/ids/10136755/Cable-HDMI-HDMI-con-Filtro-20m-20metros-Full-HD-3D-V14-Enmallado-Negro.jpg</t>
+  </si>
+  <si>
+    <t>https://daphtech.com/wp-content/uploads/2021/08/2-41.jpg</t>
+  </si>
+  <si>
+    <t>https://hftecnologia.com.ar/img/Public/1123-producto-impresora-170.jpg</t>
+  </si>
+  <si>
+    <t>https://hdmultimediaperu.com/wp-content/uploads/2023/10/Cable-de-Impresora-USB-3.0-de-1.8Mts-Delcom-DCUS090____.webp</t>
+  </si>
+  <si>
+    <t>https://infobyksystem.pe/sofsystem/files/articulos/CABLE%20USB%205MT.webp</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/5631509-1000-1000/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://www.pcware.com.co/wp-content/uploads/2023/12/gen-cable-de-poder-tipo-trebol-1.5m_11.jpg</t>
+  </si>
+  <si>
+    <t>https://credicomp.com/wp-content/uploads/2021/01/cable-pode-tipo8.jpg</t>
+  </si>
+  <si>
+    <t>https://velascostore.com/34894-thickbox_default/cable-displayport-1080p-15m.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/O7Yu2F3.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/FsXsDiC.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/dFyQel2.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/KUj9XBY.jpeg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71t331NqaNL._AC_UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71JOTuwi2HL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/47_0306060_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://gigabyte-website-production.s3.amazonaws.com/0d820e68119b5ce97f79e7286a7eb406.webp</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/120931403_01/w=1004,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://i.ebayimg.com/images/g/L~YAAOSwxMVoHSjw/s-l1200.webp</t>
+  </si>
+  <si>
+    <t>https://oechsle.vteximg.com.br/arquivos/ids/22174949-1000-1000/image-0.jpg</t>
+  </si>
+  <si>
+    <t>https://vendepe.com/wp-content/uploads/2025/06/CLAC19.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0315067_Mesa-de-trabajo-sin-logo.png</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2025/04/122_0315029_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0315025_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2025/04/117_0315116_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://images.rappi.pe/products/1756311416060_1756311413947_1756311409610.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/YiCs5FY.jpeg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/124225971_02/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/124225971_01/w=1004,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/9205998-1000-1000/image-2.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_628044-MLA99416652316_112025-O.webp</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/09/100_0315102_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/03/0305084-1.jpg</t>
+  </si>
+  <si>
+    <t>https://www.laptopcentercr.com/cdn/shop/files/w_1200_h_1200_fit_pad_1024x1024.jpg</t>
+  </si>
+  <si>
+    <t>https://coolboxpe.vtexassets.com/arquivos/ids/433846/image-775d7653677a4e30bf09229f264394d8.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/8701555/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/03/93_0315050_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://vendepe.com/wp-content/uploads/2025/06/CLAS20.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/epx6Zx7.jpeg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0315026_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0306055_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/S0480ad79fb1b4bcfbba82fb8b378fd38y.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/6677832-1000-1000/image-e23f567d4d6c40b9ab2a899c6f4bb50f.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/6123AF5UgTL._AC_UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0315043_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/tyepdBg.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/YDxmtz0.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/f9QYjZU.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/DPyJ5wq.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/prY5dh8.jpeg</t>
+  </si>
+  <si>
+    <t>https://ingcomputers.com/wp-content/uploads/2021/07/CARGADOR-DELL-PA-12-19.5v-3.34a-65W-7.4x5.0mm-PLUG-AGUJA.png</t>
+  </si>
+  <si>
+    <t>https://ingcomputers.com/wp-content/uploads/2021/07/CHARGER-DELL-19.5V-4.62A-90W-7.4X5.0MM-PLUG-AGUJA.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/9_0305013_FONBLAN-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/VI0qVOR.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/jAA2ITr.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/vQgPQzY.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/fQeBe5d.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/b7wfkfx.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/scHZT0d.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/CL8IaGk.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/3HueTe9.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/dQQsxhJ.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/UrnsGcA.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/BfFQ770.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/EH7qJHj.jpeg</t>
+  </si>
+  <si>
+    <t>https://oficomstore.com/1558-large_default/lector-de-tarjetas-hv-c304-usb.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/07/281_0304996_FONBLAN.jpg</t>
   </si>
 </sst>
 </file>
@@ -13745,7 +14126,9 @@
       <c r="C162" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D162" s="4"/>
+      <c r="D162" s="4" t="s">
+        <v>3507</v>
+      </c>
       <c r="E162" s="3">
         <v>70</v>
       </c>
@@ -14218,7 +14601,9 @@
       <c r="C187" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D187" s="4"/>
+      <c r="D187" s="4" t="s">
+        <v>3563</v>
+      </c>
       <c r="E187" s="3">
         <v>70</v>
       </c>
@@ -15806,7 +16191,9 @@
       <c r="C271" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D271" s="4"/>
+      <c r="D271" s="4" t="s">
+        <v>3437</v>
+      </c>
       <c r="E271" s="3">
         <v>85</v>
       </c>
@@ -15827,7 +16214,9 @@
       <c r="C272" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D272" s="4"/>
+      <c r="D272" s="4" t="s">
+        <v>3438</v>
+      </c>
       <c r="E272" s="3">
         <v>95</v>
       </c>
@@ -15863,7 +16252,9 @@
       <c r="C274" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D274" s="4"/>
+      <c r="D274" s="4" t="s">
+        <v>3439</v>
+      </c>
       <c r="E274" s="3">
         <v>90</v>
       </c>
@@ -15929,7 +16320,9 @@
       <c r="C278" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D278" s="4"/>
+      <c r="D278" s="4" t="s">
+        <v>3440</v>
+      </c>
       <c r="E278" s="3">
         <v>70</v>
       </c>
@@ -15965,7 +16358,9 @@
       <c r="C280" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D280" s="4"/>
+      <c r="D280" s="4" t="s">
+        <v>3441</v>
+      </c>
       <c r="E280" s="3">
         <v>95</v>
       </c>
@@ -16001,7 +16396,9 @@
       <c r="C282" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D282" s="4"/>
+      <c r="D282" s="4" t="s">
+        <v>3442</v>
+      </c>
       <c r="E282" s="3">
         <v>85</v>
       </c>
@@ -16187,7 +16584,9 @@
       <c r="C294" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D294" s="4"/>
+      <c r="D294" s="4" t="s">
+        <v>3443</v>
+      </c>
       <c r="E294" s="3">
         <v>100</v>
       </c>
@@ -16223,7 +16622,9 @@
       <c r="C296" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D296" s="4"/>
+      <c r="D296" s="4" t="s">
+        <v>3444</v>
+      </c>
       <c r="E296" s="3">
         <v>145</v>
       </c>
@@ -16364,7 +16765,9 @@
       <c r="C305" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D305" s="4"/>
+      <c r="D305" s="4" t="s">
+        <v>3445</v>
+      </c>
       <c r="E305" s="3">
         <v>65</v>
       </c>
@@ -16385,7 +16788,9 @@
       <c r="C306" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D306" s="4"/>
+      <c r="D306" s="4" t="s">
+        <v>3446</v>
+      </c>
       <c r="E306" s="3">
         <v>65</v>
       </c>
@@ -16406,7 +16811,9 @@
       <c r="C307" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D307" s="4"/>
+      <c r="D307" s="4" t="s">
+        <v>3447</v>
+      </c>
       <c r="E307" s="3">
         <v>65</v>
       </c>
@@ -16427,7 +16834,9 @@
       <c r="C308" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D308" s="4"/>
+      <c r="D308" s="4" t="s">
+        <v>3448</v>
+      </c>
       <c r="E308" s="3">
         <v>70</v>
       </c>
@@ -16448,7 +16857,9 @@
       <c r="C309" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D309" s="4"/>
+      <c r="D309" s="4" t="s">
+        <v>3452</v>
+      </c>
       <c r="E309" s="3">
         <v>100</v>
       </c>
@@ -16469,7 +16880,9 @@
       <c r="C310" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D310" s="4"/>
+      <c r="D310" s="4" t="s">
+        <v>3450</v>
+      </c>
       <c r="E310" s="3">
         <v>95</v>
       </c>
@@ -16520,7 +16933,9 @@
       <c r="C313" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D313" s="4"/>
+      <c r="D313" s="4" t="s">
+        <v>3451</v>
+      </c>
       <c r="E313" s="3">
         <v>120</v>
       </c>
@@ -16541,7 +16956,9 @@
       <c r="C314" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D314" s="4"/>
+      <c r="D314" s="4" t="s">
+        <v>3449</v>
+      </c>
       <c r="E314" s="3">
         <v>90</v>
       </c>
@@ -16592,7 +17009,9 @@
       <c r="C317" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D317" s="4"/>
+      <c r="D317" s="4" t="s">
+        <v>3453</v>
+      </c>
       <c r="E317" s="3">
         <v>95</v>
       </c>
@@ -16613,7 +17032,9 @@
       <c r="C318" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D318" s="4"/>
+      <c r="D318" s="4" t="s">
+        <v>3454</v>
+      </c>
       <c r="E318" s="3">
         <v>95</v>
       </c>
@@ -16634,7 +17055,9 @@
       <c r="C319" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D319" s="4"/>
+      <c r="D319" s="4" t="s">
+        <v>3455</v>
+      </c>
       <c r="E319" s="3">
         <v>90</v>
       </c>
@@ -16685,7 +17108,9 @@
       <c r="C322" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D322" s="4"/>
+      <c r="D322" s="4" t="s">
+        <v>3456</v>
+      </c>
       <c r="E322" s="3">
         <v>100</v>
       </c>
@@ -16706,7 +17131,9 @@
       <c r="C323" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D323" s="4"/>
+      <c r="D323" s="4" t="s">
+        <v>3457</v>
+      </c>
       <c r="E323" s="3">
         <v>85</v>
       </c>
@@ -16727,7 +17154,9 @@
       <c r="C324" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D324" s="4"/>
+      <c r="D324" s="4" t="s">
+        <v>3458</v>
+      </c>
       <c r="E324" s="3">
         <v>90</v>
       </c>
@@ -16763,7 +17192,9 @@
       <c r="C326" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D326" s="4"/>
+      <c r="D326" s="4" t="s">
+        <v>3459</v>
+      </c>
       <c r="E326" s="3">
         <v>100</v>
       </c>
@@ -16784,7 +17215,9 @@
       <c r="C327" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D327" s="4"/>
+      <c r="D327" s="4" t="s">
+        <v>3460</v>
+      </c>
       <c r="E327" s="3">
         <v>90</v>
       </c>
@@ -16805,7 +17238,9 @@
       <c r="C328" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D328" s="4"/>
+      <c r="D328" s="4" t="s">
+        <v>3461</v>
+      </c>
       <c r="E328" s="3">
         <v>90</v>
       </c>
@@ -16841,7 +17276,9 @@
       <c r="C330" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D330" s="4"/>
+      <c r="D330" s="4" t="s">
+        <v>3462</v>
+      </c>
       <c r="E330" s="3">
         <v>90</v>
       </c>
@@ -16877,7 +17314,9 @@
       <c r="C332" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D332" s="4"/>
+      <c r="D332" s="4" t="s">
+        <v>3463</v>
+      </c>
       <c r="E332" s="3">
         <v>100</v>
       </c>
@@ -16943,7 +17382,9 @@
       <c r="C336" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D336" s="4"/>
+      <c r="D336" s="4" t="s">
+        <v>3464</v>
+      </c>
       <c r="E336" s="3">
         <v>100</v>
       </c>
@@ -16964,7 +17405,9 @@
       <c r="C337" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D337" s="4"/>
+      <c r="D337" s="4" t="s">
+        <v>3465</v>
+      </c>
       <c r="E337" s="3">
         <v>105</v>
       </c>
@@ -17000,7 +17443,9 @@
       <c r="C339" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D339" s="4"/>
+      <c r="D339" s="4" t="s">
+        <v>3506</v>
+      </c>
       <c r="E339" s="3">
         <v>95</v>
       </c>
@@ -17021,7 +17466,9 @@
       <c r="C340" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D340" s="4"/>
+      <c r="D340" s="4" t="s">
+        <v>3466</v>
+      </c>
       <c r="E340" s="3">
         <v>90</v>
       </c>
@@ -17057,7 +17504,9 @@
       <c r="C342" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D342" s="4"/>
+      <c r="D342" s="4" t="s">
+        <v>3467</v>
+      </c>
       <c r="E342" s="3">
         <v>115</v>
       </c>
@@ -17078,7 +17527,9 @@
       <c r="C343" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D343" s="4"/>
+      <c r="D343" s="4" t="s">
+        <v>3506</v>
+      </c>
       <c r="E343" s="3">
         <v>120</v>
       </c>
@@ -17099,7 +17550,9 @@
       <c r="C344" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D344" s="4"/>
+      <c r="D344" s="4" t="s">
+        <v>3468</v>
+      </c>
       <c r="E344" s="3">
         <v>95</v>
       </c>
@@ -17150,7 +17603,9 @@
       <c r="C347" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D347" s="4"/>
+      <c r="D347" s="4" t="s">
+        <v>3469</v>
+      </c>
       <c r="E347" s="3">
         <v>110</v>
       </c>
@@ -17167,7 +17622,9 @@
       <c r="C348" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D348" s="4"/>
+      <c r="D348" s="4" t="s">
+        <v>3470</v>
+      </c>
       <c r="E348" s="3">
         <v>90</v>
       </c>
@@ -17233,7 +17690,9 @@
       <c r="C352" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D352" s="4"/>
+      <c r="D352" s="4" t="s">
+        <v>3471</v>
+      </c>
       <c r="E352" s="3">
         <v>130</v>
       </c>
@@ -17524,7 +17983,9 @@
       <c r="C371" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D371" s="4"/>
+      <c r="D371" s="4" t="s">
+        <v>3472</v>
+      </c>
       <c r="E371" s="3">
         <v>130</v>
       </c>
@@ -17545,7 +18006,9 @@
       <c r="C372" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D372" s="4"/>
+      <c r="D372" s="4" t="s">
+        <v>3473</v>
+      </c>
       <c r="E372" s="3">
         <v>130</v>
       </c>
@@ -17566,7 +18029,9 @@
       <c r="C373" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D373" s="4"/>
+      <c r="D373" s="4" t="s">
+        <v>3474</v>
+      </c>
       <c r="E373" s="3">
         <v>145</v>
       </c>
@@ -17917,7 +18382,9 @@
       <c r="C396" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D396" s="4"/>
+      <c r="D396" s="4" t="s">
+        <v>3475</v>
+      </c>
       <c r="E396" s="3">
         <v>65</v>
       </c>
@@ -17953,7 +18420,9 @@
       <c r="C398" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D398" s="4"/>
+      <c r="D398" s="4" t="s">
+        <v>3476</v>
+      </c>
       <c r="E398" s="3">
         <v>95</v>
       </c>
@@ -17970,7 +18439,9 @@
       <c r="C399" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D399" s="4"/>
+      <c r="D399" s="4" t="s">
+        <v>3477</v>
+      </c>
       <c r="E399" s="3">
         <v>110</v>
       </c>
@@ -17991,7 +18462,9 @@
       <c r="C400" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D400" s="4"/>
+      <c r="D400" s="4" t="s">
+        <v>3478</v>
+      </c>
       <c r="E400" s="3">
         <v>105</v>
       </c>
@@ -18027,7 +18500,9 @@
       <c r="C402" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D402" s="4"/>
+      <c r="D402" s="4" t="s">
+        <v>3479</v>
+      </c>
       <c r="E402" s="3">
         <v>105</v>
       </c>
@@ -18078,7 +18553,9 @@
       <c r="C405" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D405" s="4"/>
+      <c r="D405" s="4" t="s">
+        <v>3480</v>
+      </c>
       <c r="E405" s="3">
         <v>65</v>
       </c>
@@ -18099,7 +18576,9 @@
       <c r="C406" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D406" s="4"/>
+      <c r="D406" s="4" t="s">
+        <v>3481</v>
+      </c>
       <c r="E406" s="3">
         <v>65</v>
       </c>
@@ -18120,7 +18599,9 @@
       <c r="C407" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D407" s="4"/>
+      <c r="D407" s="4" t="s">
+        <v>3482</v>
+      </c>
       <c r="E407" s="3">
         <v>65</v>
       </c>
@@ -18141,7 +18622,9 @@
       <c r="C408" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D408" s="4"/>
+      <c r="D408" s="4" t="s">
+        <v>3483</v>
+      </c>
       <c r="E408" s="3">
         <v>65</v>
       </c>
@@ -18162,7 +18645,9 @@
       <c r="C409" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D409" s="4"/>
+      <c r="D409" s="4" t="s">
+        <v>3484</v>
+      </c>
       <c r="E409" s="3">
         <v>65</v>
       </c>
@@ -18183,7 +18668,9 @@
       <c r="C410" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D410" s="4"/>
+      <c r="D410" s="4" t="s">
+        <v>3485</v>
+      </c>
       <c r="E410" s="3">
         <v>90</v>
       </c>
@@ -18204,7 +18691,9 @@
       <c r="C411" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D411" s="4"/>
+      <c r="D411" s="4" t="s">
+        <v>3486</v>
+      </c>
       <c r="E411" s="3">
         <v>90</v>
       </c>
@@ -18328,7 +18817,9 @@
       <c r="C419" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D419" s="4"/>
+      <c r="D419" s="4" t="s">
+        <v>3508</v>
+      </c>
       <c r="E419" s="3">
         <v>100</v>
       </c>
@@ -18349,7 +18840,9 @@
       <c r="C420" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D420" s="4"/>
+      <c r="D420" s="4" t="s">
+        <v>3509</v>
+      </c>
       <c r="E420" s="3">
         <v>120</v>
       </c>
@@ -18490,7 +18983,9 @@
       <c r="C429" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D429" s="4"/>
+      <c r="D429" s="4" t="s">
+        <v>3488</v>
+      </c>
       <c r="E429" s="3">
         <v>6</v>
       </c>
@@ -18511,7 +19006,9 @@
       <c r="C430" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D430" s="4"/>
+      <c r="D430" s="4" t="s">
+        <v>3487</v>
+      </c>
       <c r="E430" s="3">
         <v>8</v>
       </c>
@@ -18532,7 +19029,9 @@
       <c r="C431" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D431" s="4"/>
+      <c r="D431" s="4" t="s">
+        <v>3489</v>
+      </c>
       <c r="E431" s="3">
         <v>9</v>
       </c>
@@ -18628,7 +19127,9 @@
       <c r="C437" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D437" s="4"/>
+      <c r="D437" s="4" t="s">
+        <v>3490</v>
+      </c>
       <c r="E437" s="3">
         <v>3</v>
       </c>
@@ -18679,7 +19180,9 @@
       <c r="C440" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D440" s="4"/>
+      <c r="D440" s="4" t="s">
+        <v>3491</v>
+      </c>
       <c r="E440" s="3">
         <v>4</v>
       </c>
@@ -18700,7 +19203,9 @@
       <c r="C441" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D441" s="4"/>
+      <c r="D441" s="5" t="s">
+        <v>3492</v>
+      </c>
       <c r="E441" s="3">
         <v>9</v>
       </c>
@@ -18781,7 +19286,9 @@
       <c r="C446" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D446" s="4"/>
+      <c r="D446" s="4" t="s">
+        <v>3493</v>
+      </c>
       <c r="E446" s="3">
         <v>7</v>
       </c>
@@ -18817,7 +19324,9 @@
       <c r="C448" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D448" s="4"/>
+      <c r="D448" s="4" t="s">
+        <v>3494</v>
+      </c>
       <c r="E448" s="3">
         <v>13</v>
       </c>
@@ -18838,7 +19347,9 @@
       <c r="C449" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D449" s="4"/>
+      <c r="D449" s="4" t="s">
+        <v>3495</v>
+      </c>
       <c r="E449" s="3">
         <v>18</v>
       </c>
@@ -18859,7 +19370,9 @@
       <c r="C450" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D450" s="4"/>
+      <c r="D450" s="4" t="s">
+        <v>3496</v>
+      </c>
       <c r="E450" s="3">
         <v>25</v>
       </c>
@@ -18880,7 +19393,9 @@
       <c r="C451" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D451" s="4"/>
+      <c r="D451" s="4" t="s">
+        <v>3497</v>
+      </c>
       <c r="E451" s="3">
         <v>35</v>
       </c>
@@ -19051,7 +19566,9 @@
       <c r="C462" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D462" s="4"/>
+      <c r="D462" s="4" t="s">
+        <v>3498</v>
+      </c>
       <c r="E462" s="3">
         <v>10</v>
       </c>
@@ -19177,7 +19694,9 @@
       <c r="C470" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D470" s="4"/>
+      <c r="D470" s="4" t="s">
+        <v>3499</v>
+      </c>
       <c r="E470" s="3">
         <v>4</v>
       </c>
@@ -19198,7 +19717,9 @@
       <c r="C471" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D471" s="4"/>
+      <c r="D471" s="4" t="s">
+        <v>3500</v>
+      </c>
       <c r="E471" s="3">
         <v>6</v>
       </c>
@@ -19219,7 +19740,9 @@
       <c r="C472" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D472" s="4"/>
+      <c r="D472" s="4" t="s">
+        <v>3501</v>
+      </c>
       <c r="E472" s="3">
         <v>9</v>
       </c>
@@ -19270,7 +19793,9 @@
       <c r="C475" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D475" s="4"/>
+      <c r="D475" s="4" t="s">
+        <v>3502</v>
+      </c>
       <c r="E475" s="3">
         <v>5</v>
       </c>
@@ -19291,7 +19816,9 @@
       <c r="C476" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D476" s="4"/>
+      <c r="D476" s="4" t="s">
+        <v>3503</v>
+      </c>
       <c r="E476" s="3">
         <v>4.5</v>
       </c>
@@ -19327,7 +19854,9 @@
       <c r="C478" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D478" s="4"/>
+      <c r="D478" s="4" t="s">
+        <v>3504</v>
+      </c>
       <c r="E478" s="3">
         <v>3</v>
       </c>
@@ -19344,7 +19873,9 @@
       <c r="C479" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="D479" s="4"/>
+      <c r="D479" s="4" t="s">
+        <v>3505</v>
+      </c>
       <c r="E479" s="3">
         <v>15</v>
       </c>
@@ -19513,7 +20044,9 @@
       <c r="C490" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="D490" s="4"/>
+      <c r="D490" s="4" t="s">
+        <v>3510</v>
+      </c>
       <c r="E490" s="3">
         <v>10</v>
       </c>
@@ -19534,7 +20067,9 @@
       <c r="C491" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="D491" s="4"/>
+      <c r="D491" s="4" t="s">
+        <v>3511</v>
+      </c>
       <c r="E491" s="3">
         <v>10</v>
       </c>
@@ -19735,7 +20270,9 @@
       <c r="C504" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="D504" s="4"/>
+      <c r="D504" s="4" t="s">
+        <v>3531</v>
+      </c>
       <c r="E504" s="3">
         <v>174</v>
       </c>
@@ -19966,7 +20503,9 @@
       <c r="C519" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D519" s="4"/>
+      <c r="D519" s="4" t="s">
+        <v>3512</v>
+      </c>
       <c r="E519" s="3">
         <v>17</v>
       </c>
@@ -19987,7 +20526,9 @@
       <c r="C520" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D520" s="4"/>
+      <c r="D520" s="4" t="s">
+        <v>3513</v>
+      </c>
       <c r="E520" s="3">
         <v>23</v>
       </c>
@@ -20023,7 +20564,9 @@
       <c r="C522" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D522" s="4"/>
+      <c r="D522" s="4" t="s">
+        <v>3514</v>
+      </c>
       <c r="E522" s="3">
         <v>22</v>
       </c>
@@ -20074,7 +20617,9 @@
       <c r="C525" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D525" s="4"/>
+      <c r="D525" s="4" t="s">
+        <v>3515</v>
+      </c>
       <c r="E525" s="3">
         <v>22</v>
       </c>
@@ -20095,7 +20640,9 @@
       <c r="C526" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D526" s="4"/>
+      <c r="D526" s="4" t="s">
+        <v>3516</v>
+      </c>
       <c r="E526" s="3">
         <v>22</v>
       </c>
@@ -20131,7 +20678,9 @@
       <c r="C528" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D528" s="4"/>
+      <c r="D528" s="4" t="s">
+        <v>3517</v>
+      </c>
       <c r="E528" s="3">
         <v>85</v>
       </c>
@@ -20152,7 +20701,9 @@
       <c r="C529" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D529" s="4"/>
+      <c r="D529" s="4" t="s">
+        <v>3518</v>
+      </c>
       <c r="E529" s="3">
         <v>95</v>
       </c>
@@ -20173,7 +20724,9 @@
       <c r="C530" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D530" s="4"/>
+      <c r="D530" s="4" t="s">
+        <v>3519</v>
+      </c>
       <c r="E530" s="3">
         <v>105</v>
       </c>
@@ -20254,7 +20807,9 @@
       <c r="C535" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D535" s="4"/>
+      <c r="D535" s="4" t="s">
+        <v>3520</v>
+      </c>
       <c r="E535" s="3">
         <v>100</v>
       </c>
@@ -20290,7 +20845,9 @@
       <c r="C537" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D537" s="4"/>
+      <c r="D537" s="4" t="s">
+        <v>3522</v>
+      </c>
       <c r="E537" s="3">
         <v>22</v>
       </c>
@@ -20311,7 +20868,9 @@
       <c r="C538" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D538" s="4"/>
+      <c r="D538" s="4" t="s">
+        <v>3523</v>
+      </c>
       <c r="E538" s="3">
         <v>22</v>
       </c>
@@ -20347,7 +20906,9 @@
       <c r="C540" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D540" s="4"/>
+      <c r="D540" s="4" t="s">
+        <v>3524</v>
+      </c>
       <c r="E540" s="3">
         <v>22</v>
       </c>
@@ -20368,7 +20929,9 @@
       <c r="C541" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D541" s="4"/>
+      <c r="D541" s="4" t="s">
+        <v>3525</v>
+      </c>
       <c r="E541" s="3">
         <v>23</v>
       </c>
@@ -20404,7 +20967,9 @@
       <c r="C543" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D543" s="4"/>
+      <c r="D543" s="4" t="s">
+        <v>3526</v>
+      </c>
       <c r="E543" s="3">
         <v>80</v>
       </c>
@@ -20425,7 +20990,9 @@
       <c r="C544" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D544" s="4"/>
+      <c r="D544" s="4" t="s">
+        <v>3527</v>
+      </c>
       <c r="E544" s="3">
         <v>30</v>
       </c>
@@ -20491,7 +21058,9 @@
       <c r="C548" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D548" s="4"/>
+      <c r="D548" s="4" t="s">
+        <v>3528</v>
+      </c>
       <c r="E548" s="3">
         <v>30</v>
       </c>
@@ -20512,7 +21081,9 @@
       <c r="C549" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D549" s="4"/>
+      <c r="D549" s="4" t="s">
+        <v>3529</v>
+      </c>
       <c r="E549" s="3">
         <v>33</v>
       </c>
@@ -20533,7 +21104,9 @@
       <c r="C550" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D550" s="4"/>
+      <c r="D550" s="4" t="s">
+        <v>3530</v>
+      </c>
       <c r="E550" s="3">
         <v>35</v>
       </c>
@@ -20569,7 +21142,9 @@
       <c r="C552" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D552" s="4"/>
+      <c r="D552" s="4" t="s">
+        <v>3529</v>
+      </c>
       <c r="E552" s="3">
         <v>35</v>
       </c>
@@ -20590,7 +21165,9 @@
       <c r="C553" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D553" s="4"/>
+      <c r="D553" s="4" t="s">
+        <v>3532</v>
+      </c>
       <c r="E553" s="3">
         <v>105</v>
       </c>
@@ -20626,7 +21203,9 @@
       <c r="C555" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D555" s="4"/>
+      <c r="D555" s="4" t="s">
+        <v>3533</v>
+      </c>
       <c r="E555" s="3">
         <v>100</v>
       </c>
@@ -20647,7 +21226,9 @@
       <c r="C556" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D556" s="4"/>
+      <c r="D556" s="4" t="s">
+        <v>3534</v>
+      </c>
       <c r="E556" s="3">
         <v>105</v>
       </c>
@@ -20668,7 +21249,9 @@
       <c r="C557" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D557" s="4"/>
+      <c r="D557" s="4" t="s">
+        <v>3535</v>
+      </c>
       <c r="E557" s="3">
         <v>115</v>
       </c>
@@ -20689,7 +21272,9 @@
       <c r="C558" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D558" s="4"/>
+      <c r="D558" s="4" t="s">
+        <v>3536</v>
+      </c>
       <c r="E558" s="3">
         <v>65</v>
       </c>
@@ -20710,7 +21295,9 @@
       <c r="C559" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D559" s="4"/>
+      <c r="D559" s="4" t="s">
+        <v>3537</v>
+      </c>
       <c r="E559" s="3">
         <v>95</v>
       </c>
@@ -20731,7 +21318,9 @@
       <c r="C560" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D560" s="4"/>
+      <c r="D560" s="4" t="s">
+        <v>3538</v>
+      </c>
       <c r="E560" s="3">
         <v>90</v>
       </c>
@@ -20752,7 +21341,9 @@
       <c r="C561" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D561" s="4"/>
+      <c r="D561" s="4" t="s">
+        <v>3539</v>
+      </c>
       <c r="E561" s="3">
         <v>35</v>
       </c>
@@ -20773,7 +21364,9 @@
       <c r="C562" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D562" s="4"/>
+      <c r="D562" s="4" t="s">
+        <v>3540</v>
+      </c>
       <c r="E562" s="3">
         <v>85</v>
       </c>
@@ -20809,7 +21402,9 @@
       <c r="C564" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D564" s="4"/>
+      <c r="D564" s="4" t="s">
+        <v>3541</v>
+      </c>
       <c r="E564" s="3">
         <v>100</v>
       </c>
@@ -20830,7 +21425,9 @@
       <c r="C565" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D565" s="4"/>
+      <c r="D565" s="4" t="s">
+        <v>3542</v>
+      </c>
       <c r="E565" s="3">
         <v>115</v>
       </c>
@@ -20851,7 +21448,9 @@
       <c r="C566" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D566" s="4"/>
+      <c r="D566" s="4" t="s">
+        <v>3543</v>
+      </c>
       <c r="E566" s="3">
         <v>100</v>
       </c>
@@ -20872,7 +21471,9 @@
       <c r="C567" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D567" s="4"/>
+      <c r="D567" s="4" t="s">
+        <v>3544</v>
+      </c>
       <c r="E567" s="3">
         <v>115</v>
       </c>
@@ -20938,7 +21539,9 @@
       <c r="C571" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D571" s="4"/>
+      <c r="D571" s="4" t="s">
+        <v>3545</v>
+      </c>
       <c r="E571" s="3">
         <v>80</v>
       </c>
@@ -21004,7 +21607,9 @@
       <c r="C575" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D575" s="4"/>
+      <c r="D575" s="4" t="s">
+        <v>3546</v>
+      </c>
       <c r="E575" s="3">
         <v>105</v>
       </c>
@@ -21040,7 +21645,9 @@
       <c r="C577" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D577" s="4"/>
+      <c r="D577" s="4" t="s">
+        <v>3547</v>
+      </c>
       <c r="E577" s="3">
         <v>22</v>
       </c>
@@ -21061,7 +21668,9 @@
       <c r="C578" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D578" s="4"/>
+      <c r="D578" s="4" t="s">
+        <v>3548</v>
+      </c>
       <c r="E578" s="3">
         <v>25</v>
       </c>
@@ -21082,7 +21691,9 @@
       <c r="C579" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D579" s="4"/>
+      <c r="D579" s="4" t="s">
+        <v>3549</v>
+      </c>
       <c r="E579" s="3">
         <v>22</v>
       </c>
@@ -21103,7 +21714,9 @@
       <c r="C580" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D580" s="4"/>
+      <c r="D580" s="4" t="s">
+        <v>3550</v>
+      </c>
       <c r="E580" s="3">
         <v>25</v>
       </c>
@@ -21124,7 +21737,9 @@
       <c r="C581" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D581" s="4"/>
+      <c r="D581" s="4" t="s">
+        <v>3551</v>
+      </c>
       <c r="E581" s="3">
         <v>22</v>
       </c>
@@ -21190,7 +21805,9 @@
       <c r="C585" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D585" s="4"/>
+      <c r="D585" s="4" t="s">
+        <v>3552</v>
+      </c>
       <c r="E585" s="3">
         <v>80</v>
       </c>
@@ -21211,7 +21828,9 @@
       <c r="C586" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D586" s="4"/>
+      <c r="D586" s="4" t="s">
+        <v>3553</v>
+      </c>
       <c r="E586" s="3">
         <v>70</v>
       </c>
@@ -21232,7 +21851,9 @@
       <c r="C587" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D587" s="4"/>
+      <c r="D587" s="4" t="s">
+        <v>3554</v>
+      </c>
       <c r="E587" s="3">
         <v>110</v>
       </c>
@@ -21253,7 +21874,9 @@
       <c r="C588" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D588" s="4"/>
+      <c r="D588" s="4" t="s">
+        <v>3555</v>
+      </c>
       <c r="E588" s="3">
         <v>80</v>
       </c>
@@ -21274,7 +21897,9 @@
       <c r="C589" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D589" s="4"/>
+      <c r="D589" s="4" t="s">
+        <v>3556</v>
+      </c>
       <c r="E589" s="3">
         <v>100</v>
       </c>
@@ -21325,7 +21950,9 @@
       <c r="C592" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D592" s="4"/>
+      <c r="D592" s="5" t="s">
+        <v>3557</v>
+      </c>
       <c r="E592" s="3">
         <v>22</v>
       </c>
@@ -21346,7 +21973,9 @@
       <c r="C593" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D593" s="4"/>
+      <c r="D593" s="5" t="s">
+        <v>3558</v>
+      </c>
       <c r="E593" s="3">
         <v>22</v>
       </c>
@@ -21367,7 +21996,9 @@
       <c r="C594" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D594" s="4"/>
+      <c r="D594" s="4" t="s">
+        <v>3559</v>
+      </c>
       <c r="E594" s="3">
         <v>22</v>
       </c>
@@ -21388,7 +22019,9 @@
       <c r="C595" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D595" s="4"/>
+      <c r="D595" s="4" t="s">
+        <v>3560</v>
+      </c>
       <c r="E595" s="3">
         <v>22</v>
       </c>
@@ -21409,7 +22042,9 @@
       <c r="C596" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D596" s="4"/>
+      <c r="D596" s="4" t="s">
+        <v>3561</v>
+      </c>
       <c r="E596" s="3">
         <v>22</v>
       </c>
@@ -21430,7 +22065,9 @@
       <c r="C597" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D597" s="4"/>
+      <c r="D597" s="4" t="s">
+        <v>3562</v>
+      </c>
       <c r="E597" s="3">
         <v>25</v>
       </c>
@@ -21886,7 +22523,9 @@
       <c r="C621" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D621" s="4"/>
+      <c r="D621" s="4" t="s">
+        <v>3521</v>
+      </c>
       <c r="E621" s="3">
         <v>28</v>
       </c>
@@ -39239,11 +39878,14 @@
     <hyperlink ref="D10" r:id="rId4" xr:uid="{AAFD1669-56D0-4FF6-8A46-5DAF64A25488}"/>
     <hyperlink ref="D9" r:id="rId5" xr:uid="{325CE0BB-7604-4D70-8DEA-280CE056D6E2}"/>
     <hyperlink ref="D27" r:id="rId6" xr:uid="{6B66D43A-9C6E-40D0-A48B-734B8766B3A6}"/>
+    <hyperlink ref="D441" r:id="rId7" xr:uid="{56C60A7B-22FE-4056-B279-2E1F623167B4}"/>
+    <hyperlink ref="D593" r:id="rId8" xr:uid="{55D0DE41-071D-4884-AA9A-CBB36ADAF9D2}"/>
+    <hyperlink ref="D592" r:id="rId9" xr:uid="{A5BC89BB-873D-44FC-8F0C-F479B62DAD2C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
--- a/isgon.xlsx
+++ b/isgon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71375BDE-1D9F-4187-BA91-31FCBB62959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3D4212-3350-4B5A-AD81-D2FC2B4C9C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{AE089D8B-92F7-455A-B330-531FF778F1FC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5125" uniqueCount="3564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5325" uniqueCount="3754">
   <si>
     <t>CODIGO</t>
   </si>
@@ -10731,6 +10731,576 @@
   </si>
   <si>
     <t>https://cahuana.com.pe/wp-content/uploads/2024/07/281_0304996_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/1Ld8nf9.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/kfDgzhz.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.ebayimg.com/images/g/2iQAAOSwIw5kZscc/s-l1200.webp</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/HxLEAcj.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/eaZ6CvR.jpeg</t>
+  </si>
+  <si>
+    <t>CLH13 CARGADOR COMPATIBLE H 19.5V 4.62A 4.5*3.0 P.AZUL</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/42Ch98f.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/OKZBOhU.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.ebayimg.com/images/g/WxcAAeSwmnBof0pa/s-l1200.webp</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/paM7WkX.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/S06XzWl.jpeg</t>
+  </si>
+  <si>
+    <t>CLH22 CARGADOR COMPATIBLE H 19.5V 3.33A 65W 4.8*1.7 PUNTA BALA</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/OGY3zm8.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/4mdxbXG.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/8JeDTz5.jpeg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/03/5_0305062_MARBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://gigabyte-website-production.s3.us-east-1.amazonaws.com/unsorted/a7fbc044690b4dede85c6a31b13de454.webp</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/03/95_0306044_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://digitalmtx.com/wp-content/uploads/Cargador-Portatil-Lenovo-Mini-20V-2A-1503-3.webp</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/29_0305018_FONBLAN-1.jpg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/123369878_03/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/36_0306048_FONBLAN_sinlogo.png</t>
+  </si>
+  <si>
+    <t>https://oechsle.vteximg.com.br/arquivos/ids/22338536-1000-1000/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/0305007.jpg</t>
+  </si>
+  <si>
+    <t>https://hiconimport.com/sistema/public/imagenes/productos/1645314448_.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/fsTGwsK.jpeg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/85_0315058_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/09/0305037_Mesa-de-trabajo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/7843553-1000-1000/image-260f18c4211f4524b2742279f3879940.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/S65eb0ef5073c4460a81099270200fda80.jpg_960x960.jpg</t>
+  </si>
+  <si>
+    <t>https://rimage.ripley.com.pe/home.ripley/Attachment/MKP/4914/PMP20000835363/full_image-1.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/gZFatCU.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/Ni2aJxN.jpeg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/50_0306058_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61Kb6Q3JaFL.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/DZtgdD2.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/mV89ULR.jpeg</t>
+  </si>
+  <si>
+    <t>CLSA1 CARGADOR COMPATIBLE SA 19V 2.1 5.0 *3.0 / 2A 6.5*4.4 NORMAL</t>
+  </si>
+  <si>
+    <t>https://compuciber.com/wp-content/uploads/2025/02/cargador-laptop-acer-punta-fina-19v-3-42a-3-0x1-1-65w-generico.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/7844714-1000-1000/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61yHWI4ufeL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://i5.walmartimages.com/asr/c242381e-2588-4c62-8fa2-2f4b13c03dae.f8dfc42cb75223007a404d8a689ea35c.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.ebayimg.com/00/s/MTYwMFgxNjAw/z/oDQAAOSwTJBi2ul1/$_57.JPG</t>
+  </si>
+  <si>
+    <t>https://image.made-in-china.com/2f0j00ecHrGgESqzku/Laptop-Adapter-AC-Power-Charger-19-5V-4-7A-6-5-4-4mm-92W-for-So-Vaio-Vgp-AC19V31.webp</t>
+  </si>
+  <si>
+    <t>https://impormel.com/wp-content/uploads/2024/03/Cargador-Hp-Mini-19v-1.58a-30w-4.8x1.7mm-Plug-Amarillo-IMPORMEL-I520704-OK.png</t>
+  </si>
+  <si>
+    <t>https://credicomp.com/wp-content/uploads/2021/01/cargador-toshiba-19v-237a-55-x-25-45w-D_NQ_NP_638352-MPE29727020083_032019-F-1.jpg</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/repuestoslaptopperu.com/wp-content/uploads/2018/11/cargador-toshiba-19v-3.42a-webp.webp</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/5264741/image-3558dd3bacee4b2088f07141a5affef2.jpg</t>
+  </si>
+  <si>
+    <t>https://gigabyte-website-production.s3.amazonaws.com/ea6de1f8e9ebafb0f45006c5ca84cd89.webp</t>
+  </si>
+  <si>
+    <t>https://i.ebayimg.com/images/g/qm8AAOSw2VVn9zXK/s-l1200.jpg</t>
+  </si>
+  <si>
+    <t>https://nsm.cl/store/3721-large_default/adaptador-cargador-ac-original-toshiba-19v-63a-55x25mm.jpg</t>
+  </si>
+  <si>
+    <t>https://compuciber.com/wp-content/uploads/2025/02/transformador-12v-3-75a-compatible.jpg</t>
+  </si>
+  <si>
+    <t>https://daphtech.com/wp-content/uploads/2022/03/CASE-2.5-USB2.0-ALUMINIO-TORNILLO_daphtech_2.jpg</t>
+  </si>
+  <si>
+    <t>https://claroperupoc.vtexassets.com/arquivos/ids/2269848/image-ba52f99563b84d819f57c691c7914e50.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/8008159/image-6b1ccca4933d44e7ac136ba3bae4af29.jpg</t>
+  </si>
+  <si>
+    <t>https://markosoft.com.ec/wp-content/uploads/2024/09/Case-Enclosure-Disco-Duro-3.5-Sata-Usb-3.0-Aluminio-Externo-1.jpg</t>
+  </si>
+  <si>
+    <t>https://sc04.alicdn.com/kf/Hf8a7b7d8ab6d407d947fe9700f870802t.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/01/88_0315034_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/11_0305032_FONBLAN-sinlogo-300x300.png</t>
+  </si>
+  <si>
+    <t>https://compuciber.com/wp-content/uploads/2024/10/cargador-monitor-lg-19v-2.1a-gen.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/02/11_0305032_FONBLAN-sinlogo.png</t>
+  </si>
+  <si>
+    <t>https://hdmultimediaperu.com/wp-content/uploads/2024/06/Adaptador-de-19V-3.42A-Para-Monitor-LG-DS18___02.webp</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/b2qJCjt.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/2w5APEm.jpeg</t>
+  </si>
+  <si>
+    <t>https://img.joomcdn.net/efa78f7f5e82944435a488a74b8ffee9af291ac9_original.jpeg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/116923132_02/w=1500,h=1500,fit=cover</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/nNf6CNg.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/I92Gvb6.jpeg</t>
+  </si>
+  <si>
+    <t>https://sofmat.com.bo/wp-content/uploads/2024/06/Cooler-Intel-12a-Generacion.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/9981-impulso-informatico.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/descargas/productos/3055-impulso-informatico.jpg</t>
+  </si>
+  <si>
+    <t>https://westor.pe/wp-content/uploads/2023/09/SS-046_1.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51GeKY76gUL.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/EmXvIxs.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.blueplanet-tec.com/wp-content/uploads/2020/08/PL-557_0.png</t>
+  </si>
+  <si>
+    <t>https://i.ytimg.com/vi/CCeE7uueC80/maxresdefault.jpg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/144414118_05/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/27612-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://mmstoreperu.com/cdn/shop/files/ESTABILIZADOR-POWER-LITE-ORION-AVR-PLI1001-4_1024x.jpg</t>
+  </si>
+  <si>
+    <t>https://rimage.ripley.com.pe/home.ripley/Attachment/MKP/3808/PMP20000710792/imagen6-1.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/7462-impulso-informatico.jpg</t>
+  </si>
+  <si>
+    <t>https://i5.walmartimages.cl/asr/da43914e-6c8c-40f2-822a-39de9eb1edf4.77e925505839a4b65511caa682a66f29.jpegh</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/7908499/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://nanotech-market.com/wp-content/uploads/2022/09/Lime-Green-and-Black-Active-Hype-Personal-Fitness-Coach-Instagram-Post-2022-10-25T170811.489.png</t>
+  </si>
+  <si>
+    <t>https://rimage.ripley.com.pe/home.ripley/Attachment/MKP/4914/PMP20000672568/imagen2-1.jpeg</t>
+  </si>
+  <si>
+    <t>https://emisoft.cuscoinformatico.com/storage/SNV3S.webp</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/8576046/image-82bdaa8a80b14f6fb35e2bd31f0185e2.jpg</t>
+  </si>
+  <si>
+    <t>https://rymportatiles.com.pe/cdn/shop/files/9261.png</t>
+  </si>
+  <si>
+    <t>https://i0.wp.com/shop.litecorp.com.ar/wp-content/uploads/2021/07/ATENCION-GAMERS-Y-MINEROS-2.jpg</t>
+  </si>
+  <si>
+    <t>https://5.imimg.com/data5/SELLER/Default/2026/2/585998936/TS/IC/CE/230284164/5e33e486-275f-4c5d-ab8d-fbc0bf8407eb.jpeg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/121180876_01/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/thumb/productos/8180-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/26428-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51fzusLjvkL._AC_SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>https://oechsle.vteximg.com.br/arquivos/ids/3065308-1000-1000/image-012cc4ff2e204b0abcd45bb707f8ebe3.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/8941356/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/xED9g93.jpeg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/h4Uh4sI.jpeg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61YxvKqz0+L.jpg</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/7483588/image-29621ae8ad264235a837b316a2aa4d44.jpg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/115654218_04/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/9296393/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/24112-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23030-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/26844-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/26671-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/thumb/productos/8042-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/thumb/productos/7992-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/25757-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://images.rappi.pe/products/1694033937819_1694033922565_1694033919460.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/25469-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/9239769-1000-1000/imageUrl_3.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/25061-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23897-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/25449-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23867-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/27261-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/thumb/productos/8087-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://avminversiones.com/wp-content/uploads/2024/09/imagen2.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23894-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/26053-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://komputer.wayraerp.pe/storage/uploads/items/AVANTY2.jpg</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_861923-MPE41067878788_032020-O.webp</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/IaYVx5B.jpeg</t>
+  </si>
+  <si>
+    <t>https://compusystemperu.com/wp-content/uploads/2021/12/M170-1.jpg</t>
+  </si>
+  <si>
+    <t>https://enjoycomputer.com.ar/wp-content/uploads/mouse-logitech-m90-dark-midnight-gray-910-004053-enjoy-computer-enjoycomputer-com-ar-4532.jpg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/17071196_1/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://oechsle.vteximg.com.br/arquivos/ids/21556010-1000-1000/image-0.jpg</t>
+  </si>
+  <si>
+    <t>https://images8.kabum.com.br/produtos/fotos/sync_mirakl/457868/xlarge/Mouse-Com-Fio-Logitech-M110-Silent-USB-Cinza-910-006757_1776096513.jpg</t>
+  </si>
+  <si>
+    <t>https://storage.googleapis.com/imagenesimpactoperu3/products/910-007456/image_1_20251212_203450_8819.webp</t>
+  </si>
+  <si>
+    <t>https://rimage.ripley.com.pe/home.ripley/Attachment/MKP/3800/PMP20000837016/imagen3-1.jpeg</t>
+  </si>
+  <si>
+    <t>https://mauricomputacion.com.ar/images/productos/19921.webp</t>
+  </si>
+  <si>
+    <t>https://cambiosystem.com/wp-content/uploads/2023/11/Pad-Mouse-Flat-Mp10.png</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/141058857_02/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://templo.com.pe/wp-content/uploads/2023/04/MOUSE-PAD-LOGITECH-G-G840-CLOTH-EXTRA-LARGE-BLACK-LOGO-1.jp</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/8UdXweF.jpeg</t>
+  </si>
+  <si>
+    <t>5.walmartimages.cl/asr/d5f67c01-9863-468b-9f26-a7c9e23919b6.8abd266f5b27bbac993dd35ce1d4e277.jpeg</t>
+  </si>
+  <si>
+    <t>https://hiconimport.com/sistema/public/imagenes/productos/1663792012_led-140-40-pines-izq-1366768-sin-ganchos.jpg</t>
+  </si>
+  <si>
+    <t>https://d2j6dbq0eux0bg.cloudfront.net/images/17416183/2078661319.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/05/3_0303042_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://konext.com.py/wp-content/uploads/2021/08/14.0-30-pin-hd.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61DXp7mrF-L.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/06/10_0303012_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/06/14_0303052_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/06/11_0303027_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/06/17_0303054_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/06/16_0303047_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://credicomp.com/wp-content/uploads/2021/01/pantallal-touch-156-led-1pantallal-touch-156-led-1sale-D_NQ_NP_824077-MLA32791610946_112019-F.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/06/7_0303021_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2023/05/2_0303020_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://credicomp.com/wp-content/uploads/2021/01/Pantalla-15.6-NT156WHM-N10-tzu-4.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2024/06/13_0303051_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://cahuana.com.pe/wp-content/uploads/2025/05/53_0303112_FONBLAN.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/27794-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/27691-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/descargas/productos/6165-impulso-informatico.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23392-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/22855-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://promart.vteximg.com.br/arquivos/ids/9243990-1000-1000/imageUrl_4.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/25227-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://plazavea.vteximg.com.br/arquivos/ids/25851733-418-418/imageUrl_1.jpg</t>
+  </si>
+  <si>
+    <t>https://westor.pe/wp-content/uploads/2024/08/ABCD.jpg</t>
+  </si>
+  <si>
+    <t>https://ae01.alicdn.com/kf/Sd820c67929c845649b151ae8ad89d7a0D.jpg</t>
+  </si>
+  <si>
+    <t>https://s3.wasabisys.com/assets.todotintasysuministros.com/assets/media/pasta-termica-disipador/pasta-termica-dorada_extraLargeThumb.webp</t>
+  </si>
+  <si>
+    <t>https://www.videoycomputacion.com.ve/8862-large_default/pasta-termica-gris-inyectadora-1gr.jpg</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/136755137_01/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/129229890_01/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/516YVqEqMBL.jpg</t>
+  </si>
+  <si>
+    <t>https://sc04.alicdn.com/kf/H107f9ed10e8d45ea9ca440b9767dcb22R.jpg</t>
+  </si>
+  <si>
+    <t>https://image.made-in-china.com/2f0j00aALoJQUFbEbq/Esonic-H81-M-2-Motherboard-LGA1150-DDR3-ATX-Mainboard-for-Intel-4th-Generation.webp</t>
+  </si>
+  <si>
+    <t>https://compuciber.com/wp-content/uploads/2025/02/placa-h110-ditipro-lga-1151-i7-i5-i3-6th-7th-8th-9th-m2-nvme-ddr4.jpg</t>
+  </si>
+  <si>
+    <t>https://daphtech.com/wp-content/uploads/2022/12/IMG_0024-scaled-1.jpg</t>
+  </si>
+  <si>
+    <t>https://compuferia.pe/wp-content/uploads/2025/12/PROTECTOR-DE-TECLADO-PARA-LAPTOP-156.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/5Lu7gDV.jpeg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61Mehbp-0FL.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/t1AvL3b.jpeg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/27859-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23138-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/27850-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/descargas/productos/5332-impulso-informatico.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/descargas/productos/5324-impulso-informatico.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/24793-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/descargas/productos/5967-impulso-informatico.jpg</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23915-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://media.falabella.com/falabellaPE/124290667_03/w=1500,h=1500,fit</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23294-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/23293-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://www.impulso.pe/imagenes/galeria/productos/27583-impulso-informatico.webp</t>
+  </si>
+  <si>
+    <t>https://oechsle.vteximg.com.br/arquivos/ids/3064289-1000-1000/image-dd87b5fdbc214140b4119d9889ff80a7.jpg</t>
+  </si>
+  <si>
+    <t>https://i.imgur.com/aKs5v61.jpeg</t>
   </si>
 </sst>
 </file>
@@ -10784,7 +11354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10807,6 +11377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -22088,7 +22659,9 @@
       <c r="C598" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D598" s="4"/>
+      <c r="D598" s="4" t="s">
+        <v>3565</v>
+      </c>
       <c r="E598" s="3">
         <v>25</v>
       </c>
@@ -22109,7 +22682,9 @@
       <c r="C599" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D599" s="4"/>
+      <c r="D599" s="4" t="s">
+        <v>3564</v>
+      </c>
       <c r="E599" s="3">
         <v>25</v>
       </c>
@@ -22130,7 +22705,9 @@
       <c r="C600" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D600" s="4"/>
+      <c r="D600" s="4" t="s">
+        <v>3566</v>
+      </c>
       <c r="E600" s="3">
         <v>65</v>
       </c>
@@ -22151,7 +22728,9 @@
       <c r="C601" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D601" s="4"/>
+      <c r="D601" s="4" t="s">
+        <v>3567</v>
+      </c>
       <c r="E601" s="3">
         <v>65</v>
       </c>
@@ -22172,7 +22751,9 @@
       <c r="C602" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D602" s="4"/>
+      <c r="D602" s="4" t="s">
+        <v>3568</v>
+      </c>
       <c r="E602" s="3">
         <v>70</v>
       </c>
@@ -22208,7 +22789,9 @@
       <c r="C604" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D604" s="4"/>
+      <c r="D604" s="8" t="s">
+        <v>3569</v>
+      </c>
       <c r="E604" s="3">
         <v>25</v>
       </c>
@@ -22229,7 +22812,9 @@
       <c r="C605" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D605" s="4"/>
+      <c r="D605" s="4" t="s">
+        <v>3570</v>
+      </c>
       <c r="E605" s="3">
         <v>90</v>
       </c>
@@ -22250,7 +22835,9 @@
       <c r="C606" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D606" s="4"/>
+      <c r="D606" s="4" t="s">
+        <v>3571</v>
+      </c>
       <c r="E606" s="3">
         <v>85</v>
       </c>
@@ -22301,7 +22888,9 @@
       <c r="C609" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D609" s="4"/>
+      <c r="D609" s="4" t="s">
+        <v>3572</v>
+      </c>
       <c r="E609" s="3">
         <v>110</v>
       </c>
@@ -22322,7 +22911,9 @@
       <c r="C610" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D610" s="4"/>
+      <c r="D610" s="4" t="s">
+        <v>3573</v>
+      </c>
       <c r="E610" s="3">
         <v>105</v>
       </c>
@@ -22343,7 +22934,9 @@
       <c r="C611" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D611" s="4"/>
+      <c r="D611" s="4" t="s">
+        <v>3574</v>
+      </c>
       <c r="E611" s="3">
         <v>95</v>
       </c>
@@ -22379,7 +22972,9 @@
       <c r="C613" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D613" s="4"/>
+      <c r="D613" s="8" t="s">
+        <v>3575</v>
+      </c>
       <c r="E613" s="3">
         <v>22</v>
       </c>
@@ -22445,7 +23040,9 @@
       <c r="C617" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D617" s="4"/>
+      <c r="D617" s="4" t="s">
+        <v>3576</v>
+      </c>
       <c r="E617" s="3">
         <v>85</v>
       </c>
@@ -22466,7 +23063,9 @@
       <c r="C618" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D618" s="4"/>
+      <c r="D618" s="4" t="s">
+        <v>3577</v>
+      </c>
       <c r="E618" s="3">
         <v>75</v>
       </c>
@@ -22487,7 +23086,9 @@
       <c r="C619" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D619" s="4"/>
+      <c r="D619" s="4" t="s">
+        <v>3578</v>
+      </c>
       <c r="E619" s="3">
         <v>50</v>
       </c>
@@ -22508,7 +23109,9 @@
       <c r="C620" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D620" s="4"/>
+      <c r="D620" s="4" t="s">
+        <v>3521</v>
+      </c>
       <c r="E620" s="3"/>
       <c r="F620" s="3"/>
       <c r="G620" s="3"/>
@@ -22523,7 +23126,7 @@
       <c r="C621" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D621" s="4" t="s">
+      <c r="D621" s="5" t="s">
         <v>3521</v>
       </c>
       <c r="E621" s="3">
@@ -22546,7 +23149,9 @@
       <c r="C622" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D622" s="4"/>
+      <c r="D622" s="4" t="s">
+        <v>3582</v>
+      </c>
       <c r="E622" s="3">
         <v>20</v>
       </c>
@@ -22563,7 +23168,9 @@
       <c r="C623" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D623" s="4"/>
+      <c r="D623" s="4" t="s">
+        <v>3584</v>
+      </c>
       <c r="E623" s="3">
         <v>25</v>
       </c>
@@ -22584,7 +23191,9 @@
       <c r="C624" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D624" s="4"/>
+      <c r="D624" s="4" t="s">
+        <v>3586</v>
+      </c>
       <c r="E624" s="3">
         <v>22</v>
       </c>
@@ -22605,7 +23214,9 @@
       <c r="C625" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D625" s="4"/>
+      <c r="D625" s="4" t="s">
+        <v>3583</v>
+      </c>
       <c r="E625" s="3">
         <v>22</v>
       </c>
@@ -22626,7 +23237,9 @@
       <c r="C626" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D626" s="4"/>
+      <c r="D626" s="4" t="s">
+        <v>3587</v>
+      </c>
       <c r="E626" s="3">
         <v>25</v>
       </c>
@@ -22647,7 +23260,9 @@
       <c r="C627" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D627" s="4"/>
+      <c r="D627" s="4" t="s">
+        <v>3588</v>
+      </c>
       <c r="E627" s="3">
         <v>22</v>
       </c>
@@ -22668,7 +23283,9 @@
       <c r="C628" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D628" s="4"/>
+      <c r="D628" s="4" t="s">
+        <v>3589</v>
+      </c>
       <c r="E628" s="3">
         <v>22</v>
       </c>
@@ -22689,7 +23306,9 @@
       <c r="C629" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D629" s="4"/>
+      <c r="D629" s="4" t="s">
+        <v>3590</v>
+      </c>
       <c r="E629" s="3">
         <v>28</v>
       </c>
@@ -22710,7 +23329,9 @@
       <c r="C630" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D630" s="4"/>
+      <c r="D630" s="4" t="s">
+        <v>3592</v>
+      </c>
       <c r="E630" s="3">
         <v>35</v>
       </c>
@@ -22731,7 +23352,9 @@
       <c r="C631" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D631" s="4"/>
+      <c r="D631" s="4" t="s">
+        <v>3591</v>
+      </c>
       <c r="E631" s="3">
         <v>28</v>
       </c>
@@ -22752,7 +23375,9 @@
       <c r="C632" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D632" s="4"/>
+      <c r="D632" s="4" t="s">
+        <v>3593</v>
+      </c>
       <c r="E632" s="3">
         <v>80</v>
       </c>
@@ -22863,7 +23488,9 @@
       <c r="C639" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D639" s="4"/>
+      <c r="D639" s="4" t="s">
+        <v>3580</v>
+      </c>
       <c r="E639" s="3">
         <v>85</v>
       </c>
@@ -22880,7 +23507,9 @@
       <c r="C640" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D640" s="4"/>
+      <c r="D640" s="4" t="s">
+        <v>3594</v>
+      </c>
       <c r="E640" s="3">
         <v>45</v>
       </c>
@@ -22901,7 +23530,9 @@
       <c r="C641" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D641" s="4"/>
+      <c r="D641" s="4" t="s">
+        <v>3579</v>
+      </c>
       <c r="E641" s="3">
         <v>60</v>
       </c>
@@ -22922,7 +23553,9 @@
       <c r="C642" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D642" s="4"/>
+      <c r="D642" s="4" t="s">
+        <v>3595</v>
+      </c>
       <c r="E642" s="3">
         <v>30</v>
       </c>
@@ -22943,7 +23576,9 @@
       <c r="C643" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D643" s="4"/>
+      <c r="D643" s="4" t="s">
+        <v>3596</v>
+      </c>
       <c r="E643" s="3">
         <v>30</v>
       </c>
@@ -22964,7 +23599,9 @@
       <c r="C644" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D644" s="4"/>
+      <c r="D644" s="4" t="s">
+        <v>3597</v>
+      </c>
       <c r="E644" s="3">
         <v>85</v>
       </c>
@@ -22985,7 +23622,9 @@
       <c r="C645" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D645" s="4"/>
+      <c r="D645" s="4" t="s">
+        <v>3585</v>
+      </c>
       <c r="E645" s="3">
         <v>80</v>
       </c>
@@ -23006,7 +23645,9 @@
       <c r="C646" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D646" s="4"/>
+      <c r="D646" s="4" t="s">
+        <v>3581</v>
+      </c>
       <c r="E646" s="3"/>
       <c r="F646" s="3"/>
       <c r="G646" s="3"/>
@@ -23021,7 +23662,9 @@
       <c r="C647" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D647" s="4"/>
+      <c r="D647" s="4" t="s">
+        <v>3598</v>
+      </c>
       <c r="E647" s="3">
         <v>120</v>
       </c>
@@ -23072,7 +23715,9 @@
       <c r="C650" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D650" s="4"/>
+      <c r="D650" s="4" t="s">
+        <v>3599</v>
+      </c>
       <c r="E650" s="3">
         <v>55</v>
       </c>
@@ -23108,7 +23753,9 @@
       <c r="C652" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D652" s="4"/>
+      <c r="D652" s="4" t="s">
+        <v>3600</v>
+      </c>
       <c r="E652" s="3">
         <v>90</v>
       </c>
@@ -23174,7 +23821,9 @@
       <c r="C656" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D656" s="4"/>
+      <c r="D656" s="8" t="s">
+        <v>3601</v>
+      </c>
       <c r="E656" s="3">
         <v>25</v>
       </c>
@@ -23195,7 +23844,9 @@
       <c r="C657" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D657" s="4"/>
+      <c r="D657" s="4" t="s">
+        <v>3602</v>
+      </c>
       <c r="E657" s="3">
         <v>22</v>
       </c>
@@ -23216,7 +23867,9 @@
       <c r="C658" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D658" s="4"/>
+      <c r="D658" s="4" t="s">
+        <v>3603</v>
+      </c>
       <c r="E658" s="3">
         <v>22</v>
       </c>
@@ -23237,7 +23890,9 @@
       <c r="C659" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D659" s="4"/>
+      <c r="D659" s="4" t="s">
+        <v>3604</v>
+      </c>
       <c r="E659" s="3">
         <v>28</v>
       </c>
@@ -23258,7 +23913,9 @@
       <c r="C660" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D660" s="4"/>
+      <c r="D660" s="4" t="s">
+        <v>3605</v>
+      </c>
       <c r="E660" s="3">
         <v>22</v>
       </c>
@@ -23279,7 +23936,9 @@
       <c r="C661" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D661" s="4"/>
+      <c r="D661" s="4" t="s">
+        <v>3606</v>
+      </c>
       <c r="E661" s="3">
         <v>22</v>
       </c>
@@ -23300,7 +23959,9 @@
       <c r="C662" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D662" s="4"/>
+      <c r="D662" s="4" t="s">
+        <v>3607</v>
+      </c>
       <c r="E662" s="3">
         <v>28</v>
       </c>
@@ -23336,7 +23997,9 @@
       <c r="C664" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D664" s="4"/>
+      <c r="D664" s="4" t="s">
+        <v>3608</v>
+      </c>
       <c r="E664" s="3">
         <v>25</v>
       </c>
@@ -23357,7 +24020,9 @@
       <c r="C665" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D665" s="4"/>
+      <c r="D665" s="4" t="s">
+        <v>3609</v>
+      </c>
       <c r="E665" s="3">
         <v>22</v>
       </c>
@@ -23378,7 +24043,9 @@
       <c r="C666" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D666" s="4"/>
+      <c r="D666" s="4" t="s">
+        <v>3610</v>
+      </c>
       <c r="E666" s="3">
         <v>22</v>
       </c>
@@ -23399,7 +24066,9 @@
       <c r="C667" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D667" s="4"/>
+      <c r="D667" s="4" t="s">
+        <v>3612</v>
+      </c>
       <c r="E667" s="3">
         <v>22</v>
       </c>
@@ -23420,7 +24089,9 @@
       <c r="C668" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D668" s="4"/>
+      <c r="D668" s="4" t="s">
+        <v>3613</v>
+      </c>
       <c r="E668" s="3">
         <v>30</v>
       </c>
@@ -23441,7 +24112,9 @@
       <c r="C669" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D669" s="4"/>
+      <c r="D669" s="4" t="s">
+        <v>3614</v>
+      </c>
       <c r="E669" s="3">
         <v>70</v>
       </c>
@@ -23462,7 +24135,9 @@
       <c r="C670" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D670" s="4"/>
+      <c r="D670" s="4" t="s">
+        <v>3611</v>
+      </c>
       <c r="E670" s="3">
         <v>22</v>
       </c>
@@ -23573,7 +24248,9 @@
       <c r="C677" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D677" s="4"/>
+      <c r="D677" s="4" t="s">
+        <v>3615</v>
+      </c>
       <c r="E677" s="3">
         <v>22</v>
       </c>
@@ -23590,7 +24267,9 @@
       <c r="C678" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D678" s="4"/>
+      <c r="D678" s="4" t="s">
+        <v>3621</v>
+      </c>
       <c r="E678" s="3">
         <v>22</v>
       </c>
@@ -23626,7 +24305,9 @@
       <c r="C680" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D680" s="4"/>
+      <c r="D680" s="4" t="s">
+        <v>3622</v>
+      </c>
       <c r="E680" s="3">
         <v>22</v>
       </c>
@@ -23662,7 +24343,9 @@
       <c r="C682" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D682" s="4"/>
+      <c r="D682" s="4" t="s">
+        <v>3623</v>
+      </c>
       <c r="E682" s="3">
         <v>22</v>
       </c>
@@ -23683,7 +24366,9 @@
       <c r="C683" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D683" s="4"/>
+      <c r="D683" s="4" t="s">
+        <v>3624</v>
+      </c>
       <c r="E683" s="3">
         <v>22</v>
       </c>
@@ -23704,7 +24389,9 @@
       <c r="C684" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D684" s="4"/>
+      <c r="D684" s="4" t="s">
+        <v>3625</v>
+      </c>
       <c r="E684" s="3">
         <v>22</v>
       </c>
@@ -23770,7 +24457,9 @@
       <c r="C688" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D688" s="4"/>
+      <c r="D688" s="4" t="s">
+        <v>3626</v>
+      </c>
       <c r="E688" s="3">
         <v>80</v>
       </c>
@@ -23806,7 +24495,9 @@
       <c r="C690" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D690" s="4"/>
+      <c r="D690" s="4" t="s">
+        <v>3627</v>
+      </c>
       <c r="E690" s="3">
         <v>18</v>
       </c>
@@ -23824,7 +24515,9 @@
       <c r="B691" s="4" t="s">
         <v>1387</v>
       </c>
-      <c r="C691" s="2"/>
+      <c r="C691" s="2" t="s">
+        <v>989</v>
+      </c>
       <c r="D691" s="4"/>
       <c r="E691" s="3"/>
       <c r="F691" s="3"/>
@@ -23840,7 +24533,9 @@
       <c r="C692" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D692" s="4"/>
+      <c r="D692" s="4" t="s">
+        <v>3628</v>
+      </c>
       <c r="E692" s="3">
         <v>85</v>
       </c>
@@ -23861,7 +24556,9 @@
       <c r="C693" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D693" s="4"/>
+      <c r="D693" s="4" t="s">
+        <v>3629</v>
+      </c>
       <c r="E693" s="3">
         <v>85</v>
       </c>
@@ -23882,7 +24579,9 @@
       <c r="C694" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D694" s="4"/>
+      <c r="D694" s="4" t="s">
+        <v>3628</v>
+      </c>
       <c r="E694" s="3">
         <v>80</v>
       </c>
@@ -23948,7 +24647,9 @@
       <c r="C698" s="2" t="s">
         <v>1402</v>
       </c>
-      <c r="D698" s="4"/>
+      <c r="D698" s="4" t="s">
+        <v>3616</v>
+      </c>
       <c r="E698" s="3">
         <v>14</v>
       </c>
@@ -23969,7 +24670,9 @@
       <c r="C699" s="2" t="s">
         <v>1402</v>
       </c>
-      <c r="D699" s="4"/>
+      <c r="D699" s="4" t="s">
+        <v>3617</v>
+      </c>
       <c r="E699" s="3">
         <v>22</v>
       </c>
@@ -23990,7 +24693,9 @@
       <c r="C700" s="2" t="s">
         <v>1402</v>
       </c>
-      <c r="D700" s="4"/>
+      <c r="D700" s="4" t="s">
+        <v>3618</v>
+      </c>
       <c r="E700" s="3">
         <v>65</v>
       </c>
@@ -24011,7 +24716,9 @@
       <c r="C701" s="2" t="s">
         <v>1402</v>
       </c>
-      <c r="D701" s="4"/>
+      <c r="D701" s="4" t="s">
+        <v>3619</v>
+      </c>
       <c r="E701" s="3">
         <v>70</v>
       </c>
@@ -24028,7 +24735,9 @@
       <c r="C702" s="2" t="s">
         <v>1402</v>
       </c>
-      <c r="D702" s="4"/>
+      <c r="D702" s="4" t="s">
+        <v>3620</v>
+      </c>
       <c r="E702" s="3">
         <v>45</v>
       </c>
@@ -24079,7 +24788,9 @@
       <c r="C705" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="D705" s="4"/>
+      <c r="D705" s="4" t="s">
+        <v>3630</v>
+      </c>
       <c r="E705" s="3">
         <v>40</v>
       </c>
@@ -24100,7 +24811,9 @@
       <c r="C706" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="D706" s="4"/>
+      <c r="D706" s="4" t="s">
+        <v>3631</v>
+      </c>
       <c r="E706" s="3">
         <v>40</v>
       </c>
@@ -24897,7 +25610,9 @@
       <c r="C759" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="D759" s="4"/>
+      <c r="D759" s="4" t="s">
+        <v>3632</v>
+      </c>
       <c r="E759" s="3">
         <v>25</v>
       </c>
@@ -24916,7 +25631,9 @@
       <c r="C760" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="D760" s="4"/>
+      <c r="D760" s="4" t="s">
+        <v>3633</v>
+      </c>
       <c r="E760" s="3">
         <v>6</v>
       </c>
@@ -24967,7 +25684,9 @@
       <c r="C763" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="D763" s="4"/>
+      <c r="D763" s="4" t="s">
+        <v>3634</v>
+      </c>
       <c r="E763" s="3">
         <v>16</v>
       </c>
@@ -25314,7 +26033,9 @@
       <c r="C786" s="2" t="s">
         <v>1579</v>
       </c>
-      <c r="D786" s="4"/>
+      <c r="D786" s="4" t="s">
+        <v>3635</v>
+      </c>
       <c r="E786" s="3">
         <v>20</v>
       </c>
@@ -25335,7 +26056,9 @@
       <c r="C787" s="2" t="s">
         <v>1579</v>
       </c>
-      <c r="D787" s="4"/>
+      <c r="D787" s="4" t="s">
+        <v>3636</v>
+      </c>
       <c r="E787" s="3">
         <v>18</v>
       </c>
@@ -25356,7 +26079,9 @@
       <c r="C788" s="2" t="s">
         <v>1579</v>
       </c>
-      <c r="D788" s="4"/>
+      <c r="D788" s="4" t="s">
+        <v>3637</v>
+      </c>
       <c r="E788" s="3">
         <v>30</v>
       </c>
@@ -25377,7 +26102,9 @@
       <c r="C789" s="2" t="s">
         <v>1586</v>
       </c>
-      <c r="D789" s="4"/>
+      <c r="D789" s="4" t="s">
+        <v>3638</v>
+      </c>
       <c r="E789" s="3">
         <v>22</v>
       </c>
@@ -25443,7 +26170,9 @@
       <c r="C793" s="2" t="s">
         <v>1592</v>
       </c>
-      <c r="D793" s="4"/>
+      <c r="D793" s="4" t="s">
+        <v>3639</v>
+      </c>
       <c r="E793" s="3">
         <v>60</v>
       </c>
@@ -25475,7 +26204,9 @@
       <c r="C795" s="2" t="s">
         <v>1592</v>
       </c>
-      <c r="D795" s="4"/>
+      <c r="D795" s="4" t="s">
+        <v>3640</v>
+      </c>
       <c r="E795" s="3">
         <v>55</v>
       </c>
@@ -25511,7 +26242,9 @@
       <c r="C797" s="2" t="s">
         <v>1592</v>
       </c>
-      <c r="D797" s="4"/>
+      <c r="D797" s="4" t="s">
+        <v>3641</v>
+      </c>
       <c r="E797" s="3">
         <v>60</v>
       </c>
@@ -25528,7 +26261,9 @@
       <c r="C798" s="2" t="s">
         <v>1592</v>
       </c>
-      <c r="D798" s="4"/>
+      <c r="D798" s="4" t="s">
+        <v>3642</v>
+      </c>
       <c r="E798" s="3">
         <v>50</v>
       </c>
@@ -25575,7 +26310,9 @@
       <c r="C801" s="2" t="s">
         <v>1613</v>
       </c>
-      <c r="D801" s="4"/>
+      <c r="D801" s="4" t="s">
+        <v>3643</v>
+      </c>
       <c r="E801" s="3">
         <v>48</v>
       </c>
@@ -25626,7 +26363,9 @@
       <c r="C804" s="2" t="s">
         <v>1613</v>
       </c>
-      <c r="D804" s="4"/>
+      <c r="D804" s="4" t="s">
+        <v>3644</v>
+      </c>
       <c r="E804" s="3">
         <v>60</v>
       </c>
@@ -25658,7 +26397,9 @@
       <c r="C806" s="2" t="s">
         <v>1622</v>
       </c>
-      <c r="D806" s="4"/>
+      <c r="D806" s="4" t="s">
+        <v>3645</v>
+      </c>
       <c r="E806" s="3">
         <v>13</v>
       </c>
@@ -25679,7 +26420,9 @@
       <c r="C807" s="2" t="s">
         <v>1622</v>
       </c>
-      <c r="D807" s="4"/>
+      <c r="D807" s="4" t="s">
+        <v>3646</v>
+      </c>
       <c r="E807" s="3">
         <v>13</v>
       </c>
@@ -25996,7 +26739,9 @@
       <c r="C828" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="D828" s="4"/>
+      <c r="D828" s="4" t="s">
+        <v>3647</v>
+      </c>
       <c r="E828" s="3">
         <v>230</v>
       </c>
@@ -26013,7 +26758,9 @@
       <c r="C829" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="D829" s="4"/>
+      <c r="D829" s="4" t="s">
+        <v>3648</v>
+      </c>
       <c r="E829" s="3">
         <v>430</v>
       </c>
@@ -26030,7 +26777,9 @@
       <c r="C830" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="D830" s="4"/>
+      <c r="D830" s="4" t="s">
+        <v>3650</v>
+      </c>
       <c r="E830" s="3">
         <v>520</v>
       </c>
@@ -26137,7 +26886,9 @@
       <c r="C837" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="D837" s="4"/>
+      <c r="D837" s="4" t="s">
+        <v>3651</v>
+      </c>
       <c r="E837" s="3">
         <v>425</v>
       </c>
@@ -26154,7 +26905,9 @@
       <c r="C838" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="D838" s="4"/>
+      <c r="D838" s="4" t="s">
+        <v>3649</v>
+      </c>
       <c r="E838" s="3">
         <v>600</v>
       </c>
@@ -26201,7 +26954,9 @@
       <c r="C841" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="D841" s="4"/>
+      <c r="D841" s="4" t="s">
+        <v>3652</v>
+      </c>
       <c r="E841" s="3">
         <v>280</v>
       </c>
@@ -26263,7 +27018,9 @@
       <c r="C845" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="D845" s="4"/>
+      <c r="D845" s="4" t="s">
+        <v>3653</v>
+      </c>
       <c r="E845" s="3">
         <v>180</v>
       </c>
@@ -26280,7 +27037,9 @@
       <c r="C846" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="D846" s="4"/>
+      <c r="D846" s="4" t="s">
+        <v>3654</v>
+      </c>
       <c r="E846" s="3">
         <v>280</v>
       </c>
@@ -26507,7 +27266,9 @@
       <c r="C861" s="2" t="s">
         <v>1730</v>
       </c>
-      <c r="D861" s="4"/>
+      <c r="D861" s="4" t="s">
+        <v>3656</v>
+      </c>
       <c r="E861" s="3">
         <v>20</v>
       </c>
@@ -26543,7 +27304,9 @@
       <c r="C863" s="2" t="s">
         <v>1730</v>
       </c>
-      <c r="D863" s="4"/>
+      <c r="D863" s="4" t="s">
+        <v>3657</v>
+      </c>
       <c r="E863" s="3">
         <v>20</v>
       </c>
@@ -26579,7 +27342,9 @@
       <c r="C865" s="2" t="s">
         <v>1730</v>
       </c>
-      <c r="D865" s="4"/>
+      <c r="D865" s="4" t="s">
+        <v>3655</v>
+      </c>
       <c r="E865" s="3">
         <v>22</v>
       </c>
@@ -26630,7 +27395,9 @@
       <c r="C868" s="2" t="s">
         <v>1755</v>
       </c>
-      <c r="D868" s="4"/>
+      <c r="D868" s="4" t="s">
+        <v>3658</v>
+      </c>
       <c r="E868" s="3">
         <v>35</v>
       </c>
@@ -26711,7 +27478,9 @@
       <c r="C873" s="2" t="s">
         <v>1761</v>
       </c>
-      <c r="D873" s="4"/>
+      <c r="D873" s="4" t="s">
+        <v>3659</v>
+      </c>
       <c r="E873" s="3">
         <v>30</v>
       </c>
@@ -26732,7 +27501,9 @@
       <c r="C874" s="2" t="s">
         <v>1761</v>
       </c>
-      <c r="D874" s="4"/>
+      <c r="D874" s="4" t="s">
+        <v>3660</v>
+      </c>
       <c r="E874" s="3">
         <v>30</v>
       </c>
@@ -26764,7 +27535,9 @@
       <c r="C876" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="D876" s="4"/>
+      <c r="D876" s="4" t="s">
+        <v>3661</v>
+      </c>
       <c r="E876" s="3">
         <v>80</v>
       </c>
@@ -26785,7 +27558,9 @@
       <c r="C877" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="D877" s="4"/>
+      <c r="D877" s="4" t="s">
+        <v>3662</v>
+      </c>
       <c r="E877" s="3">
         <v>110</v>
       </c>
@@ -26823,7 +27598,9 @@
       <c r="C879" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="D879" s="4"/>
+      <c r="D879" s="4" t="s">
+        <v>3664</v>
+      </c>
       <c r="E879" s="3">
         <v>110</v>
       </c>
@@ -26859,7 +27636,9 @@
       <c r="C881" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="D881" s="4"/>
+      <c r="D881" s="4" t="s">
+        <v>3665</v>
+      </c>
       <c r="E881" s="3">
         <v>180</v>
       </c>
@@ -26910,7 +27689,9 @@
       <c r="C884" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="D884" s="4"/>
+      <c r="D884" s="4" t="s">
+        <v>3663</v>
+      </c>
       <c r="E884" s="3">
         <v>60</v>
       </c>
@@ -27414,7 +28195,9 @@
       <c r="C916" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D916" s="4"/>
+      <c r="D916" s="4" t="s">
+        <v>3666</v>
+      </c>
       <c r="E916" s="3">
         <v>35</v>
       </c>
@@ -27435,7 +28218,9 @@
       <c r="C917" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D917" s="4"/>
+      <c r="D917" s="4" t="s">
+        <v>3667</v>
+      </c>
       <c r="E917" s="3">
         <v>35</v>
       </c>
@@ -27471,7 +28256,9 @@
       <c r="C919" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D919" s="4"/>
+      <c r="D919" s="4" t="s">
+        <v>3668</v>
+      </c>
       <c r="E919" s="3">
         <v>35</v>
       </c>
@@ -27492,7 +28279,9 @@
       <c r="C920" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D920" s="4"/>
+      <c r="D920" s="4" t="s">
+        <v>3669</v>
+      </c>
       <c r="E920" s="3">
         <v>18</v>
       </c>
@@ -27528,7 +28317,9 @@
       <c r="C922" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D922" s="4"/>
+      <c r="D922" s="4" t="s">
+        <v>3670</v>
+      </c>
       <c r="E922" s="3">
         <v>18</v>
       </c>
@@ -27579,7 +28370,9 @@
       <c r="C925" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D925" s="4"/>
+      <c r="D925" s="4" t="s">
+        <v>3671</v>
+      </c>
       <c r="E925" s="3">
         <v>17</v>
       </c>
@@ -27630,7 +28423,9 @@
       <c r="C928" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D928" s="4"/>
+      <c r="D928" s="4" t="s">
+        <v>3672</v>
+      </c>
       <c r="E928" s="3">
         <v>15</v>
       </c>
@@ -27651,7 +28446,9 @@
       <c r="C929" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D929" s="4"/>
+      <c r="D929" s="4" t="s">
+        <v>3673</v>
+      </c>
       <c r="E929" s="3">
         <v>16</v>
       </c>
@@ -27672,7 +28469,9 @@
       <c r="C930" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D930" s="4"/>
+      <c r="D930" s="4" t="s">
+        <v>3674</v>
+      </c>
       <c r="E930" s="3">
         <v>15</v>
       </c>
@@ -27693,7 +28492,9 @@
       <c r="C931" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D931" s="4"/>
+      <c r="D931" s="4" t="s">
+        <v>3675</v>
+      </c>
       <c r="E931" s="3">
         <v>14</v>
       </c>
@@ -27804,7 +28605,9 @@
       <c r="C938" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D938" s="4"/>
+      <c r="D938" s="4" t="s">
+        <v>3676</v>
+      </c>
       <c r="E938" s="3">
         <v>20</v>
       </c>
@@ -27840,7 +28643,9 @@
       <c r="C940" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D940" s="4"/>
+      <c r="D940" s="4" t="s">
+        <v>3677</v>
+      </c>
       <c r="E940" s="3">
         <v>20</v>
       </c>
@@ -27861,7 +28666,9 @@
       <c r="C941" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D941" s="4"/>
+      <c r="D941" s="4" t="s">
+        <v>3678</v>
+      </c>
       <c r="E941" s="3">
         <v>28</v>
       </c>
@@ -27987,7 +28794,9 @@
       <c r="C949" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D949" s="4"/>
+      <c r="D949" s="4" t="s">
+        <v>3679</v>
+      </c>
       <c r="E949" s="3">
         <v>15</v>
       </c>
@@ -28068,7 +28877,9 @@
       <c r="C954" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D954" s="4"/>
+      <c r="D954" s="4" t="s">
+        <v>3680</v>
+      </c>
       <c r="E954" s="3">
         <v>15</v>
       </c>
@@ -28086,8 +28897,12 @@
       <c r="B955" s="2" t="s">
         <v>1933</v>
       </c>
-      <c r="C955" s="2"/>
-      <c r="D955" s="4"/>
+      <c r="C955" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D955" s="4" t="s">
+        <v>3681</v>
+      </c>
       <c r="E955" s="3">
         <v>19</v>
       </c>
@@ -28105,8 +28920,12 @@
       <c r="B956" s="2" t="s">
         <v>1935</v>
       </c>
-      <c r="C956" s="2"/>
-      <c r="D956" s="4"/>
+      <c r="C956" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D956" s="4" t="s">
+        <v>3682</v>
+      </c>
       <c r="E956" s="3">
         <v>19</v>
       </c>
@@ -28124,8 +28943,12 @@
       <c r="B957" s="2" t="s">
         <v>1937</v>
       </c>
-      <c r="C957" s="2"/>
-      <c r="D957" s="4"/>
+      <c r="C957" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D957" s="4" t="s">
+        <v>3683</v>
+      </c>
       <c r="E957" s="3">
         <v>15</v>
       </c>
@@ -28143,8 +28966,12 @@
       <c r="B958" s="2" t="s">
         <v>1939</v>
       </c>
-      <c r="C958" s="2"/>
-      <c r="D958" s="4"/>
+      <c r="C958" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D958" s="4" t="s">
+        <v>3684</v>
+      </c>
       <c r="E958" s="3">
         <v>15</v>
       </c>
@@ -28315,7 +29142,9 @@
       <c r="C969" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D969" s="4"/>
+      <c r="D969" s="4" t="s">
+        <v>3685</v>
+      </c>
       <c r="E969" s="3">
         <v>50</v>
       </c>
@@ -28332,7 +29161,9 @@
       <c r="C970" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D970" s="4"/>
+      <c r="D970" s="4" t="s">
+        <v>3686</v>
+      </c>
       <c r="E970" s="3">
         <v>68</v>
       </c>
@@ -28529,7 +29360,9 @@
       <c r="C983" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D983" s="4"/>
+      <c r="D983" s="4" t="s">
+        <v>3687</v>
+      </c>
       <c r="E983" s="3">
         <v>33</v>
       </c>
@@ -28576,7 +29409,9 @@
       <c r="C986" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D986" s="4"/>
+      <c r="D986" s="4" t="s">
+        <v>3688</v>
+      </c>
       <c r="E986" s="3">
         <v>41</v>
       </c>
@@ -28597,7 +29432,9 @@
       <c r="C987" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D987" s="4"/>
+      <c r="D987" s="4" t="s">
+        <v>3689</v>
+      </c>
       <c r="E987" s="3">
         <v>26</v>
       </c>
@@ -28618,7 +29455,9 @@
       <c r="C988" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D988" s="4"/>
+      <c r="D988" s="4" t="s">
+        <v>3690</v>
+      </c>
       <c r="E988" s="3">
         <v>48</v>
       </c>
@@ -28639,7 +29478,9 @@
       <c r="C989" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D989" s="4"/>
+      <c r="D989" s="4" t="s">
+        <v>3691</v>
+      </c>
       <c r="E989" s="3"/>
       <c r="F989" s="3"/>
       <c r="G989" s="3"/>
@@ -28654,7 +29495,9 @@
       <c r="C990" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D990" s="4"/>
+      <c r="D990" s="4" t="s">
+        <v>3692</v>
+      </c>
       <c r="E990" s="3">
         <v>31</v>
       </c>
@@ -28705,7 +29548,9 @@
       <c r="C993" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D993" s="4"/>
+      <c r="D993" s="4" t="s">
+        <v>3693</v>
+      </c>
       <c r="E993" s="3">
         <v>46</v>
       </c>
@@ -28726,7 +29571,9 @@
       <c r="C994" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="D994" s="4"/>
+      <c r="D994" s="4" t="s">
+        <v>3694</v>
+      </c>
       <c r="E994" s="3">
         <v>46</v>
       </c>
@@ -28989,7 +29836,9 @@
       <c r="C1011" s="2" t="s">
         <v>2048</v>
       </c>
-      <c r="D1011" s="4"/>
+      <c r="D1011" s="4" t="s">
+        <v>3695</v>
+      </c>
       <c r="E1011" s="3">
         <v>4.5</v>
       </c>
@@ -29010,7 +29859,9 @@
       <c r="C1012" s="2" t="s">
         <v>2048</v>
       </c>
-      <c r="D1012" s="4"/>
+      <c r="D1012" s="4" t="s">
+        <v>3696</v>
+      </c>
       <c r="E1012" s="3">
         <v>3.5</v>
       </c>
@@ -29046,7 +29897,9 @@
       <c r="C1014" s="2" t="s">
         <v>2048</v>
       </c>
-      <c r="D1014" s="4"/>
+      <c r="D1014" s="4" t="s">
+        <v>3698</v>
+      </c>
       <c r="E1014" s="3">
         <v>15</v>
       </c>
@@ -29067,7 +29920,9 @@
       <c r="C1015" s="2" t="s">
         <v>2048</v>
       </c>
-      <c r="D1015" s="4"/>
+      <c r="D1015" s="4" t="s">
+        <v>3699</v>
+      </c>
       <c r="E1015" s="3">
         <v>14</v>
       </c>
@@ -29088,7 +29943,9 @@
       <c r="C1016" s="2" t="s">
         <v>2048</v>
       </c>
-      <c r="D1016" s="4"/>
+      <c r="D1016" s="4" t="s">
+        <v>3697</v>
+      </c>
       <c r="E1016" s="3"/>
       <c r="F1016" s="3"/>
       <c r="G1016" s="3"/>
@@ -29103,7 +29960,9 @@
       <c r="C1017" s="2" t="s">
         <v>2048</v>
       </c>
-      <c r="D1017" s="4"/>
+      <c r="D1017" s="4" t="s">
+        <v>3700</v>
+      </c>
       <c r="E1017" s="3">
         <v>8</v>
       </c>
@@ -29210,7 +30069,9 @@
       <c r="C1024" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1024" s="4"/>
+      <c r="D1024" s="4" t="s">
+        <v>3701</v>
+      </c>
       <c r="E1024" s="3">
         <v>95</v>
       </c>
@@ -29231,7 +30092,9 @@
       <c r="C1025" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1025" s="4"/>
+      <c r="D1025" s="4" t="s">
+        <v>3702</v>
+      </c>
       <c r="E1025" s="3">
         <v>110</v>
       </c>
@@ -29372,7 +30235,9 @@
       <c r="C1034" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1034" s="4"/>
+      <c r="D1034" s="4" t="s">
+        <v>3705</v>
+      </c>
       <c r="E1034" s="3">
         <v>145</v>
       </c>
@@ -29393,7 +30258,9 @@
       <c r="C1035" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1035" s="4"/>
+      <c r="D1035" s="4" t="s">
+        <v>3706</v>
+      </c>
       <c r="E1035" s="3">
         <v>155</v>
       </c>
@@ -29414,7 +30281,9 @@
       <c r="C1036" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1036" s="4"/>
+      <c r="D1036" s="4" t="s">
+        <v>3707</v>
+      </c>
       <c r="E1036" s="3">
         <v>250</v>
       </c>
@@ -29551,7 +30420,9 @@
       <c r="C1045" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1045" s="4"/>
+      <c r="D1045" s="4" t="s">
+        <v>3704</v>
+      </c>
       <c r="E1045" s="3">
         <v>135</v>
       </c>
@@ -29572,7 +30443,9 @@
       <c r="C1046" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1046" s="4"/>
+      <c r="D1046" s="4" t="s">
+        <v>3703</v>
+      </c>
       <c r="E1046" s="3">
         <v>135</v>
       </c>
@@ -29608,7 +30481,9 @@
       <c r="C1048" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1048" s="4"/>
+      <c r="D1048" s="4" t="s">
+        <v>3708</v>
+      </c>
       <c r="E1048" s="3">
         <v>180</v>
       </c>
@@ -29674,7 +30549,9 @@
       <c r="C1052" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1052" s="4"/>
+      <c r="D1052" s="4" t="s">
+        <v>3709</v>
+      </c>
       <c r="E1052" s="3">
         <v>190</v>
       </c>
@@ -29695,7 +30572,9 @@
       <c r="C1053" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1053" s="4"/>
+      <c r="D1053" s="4" t="s">
+        <v>3711</v>
+      </c>
       <c r="E1053" s="3">
         <v>135</v>
       </c>
@@ -29716,7 +30595,9 @@
       <c r="C1054" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1054" s="4"/>
+      <c r="D1054" s="4" t="s">
+        <v>3713</v>
+      </c>
       <c r="E1054" s="3">
         <v>135</v>
       </c>
@@ -29737,7 +30618,9 @@
       <c r="C1055" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1055" s="4"/>
+      <c r="D1055" s="4" t="s">
+        <v>3712</v>
+      </c>
       <c r="E1055" s="3">
         <v>185</v>
       </c>
@@ -29758,7 +30641,9 @@
       <c r="C1056" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1056" s="4"/>
+      <c r="D1056" s="4" t="s">
+        <v>3714</v>
+      </c>
       <c r="E1056" s="3">
         <v>190</v>
       </c>
@@ -29779,7 +30664,9 @@
       <c r="C1057" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1057" s="4"/>
+      <c r="D1057" s="4" t="s">
+        <v>3715</v>
+      </c>
       <c r="E1057" s="3">
         <v>205</v>
       </c>
@@ -29800,7 +30687,9 @@
       <c r="C1058" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1058" s="4"/>
+      <c r="D1058" s="4" t="s">
+        <v>3710</v>
+      </c>
       <c r="E1058" s="3">
         <v>205</v>
       </c>
@@ -29836,7 +30725,9 @@
       <c r="C1060" s="2" t="s">
         <v>2075</v>
       </c>
-      <c r="D1060" s="4"/>
+      <c r="D1060" s="4" t="s">
+        <v>3716</v>
+      </c>
       <c r="E1060" s="3">
         <v>250</v>
       </c>
@@ -30185,7 +31076,9 @@
       <c r="C1083" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="D1083" s="4"/>
+      <c r="D1083" s="4" t="s">
+        <v>3717</v>
+      </c>
       <c r="E1083" s="3">
         <v>45</v>
       </c>
@@ -30202,7 +31095,9 @@
       <c r="C1084" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="D1084" s="4"/>
+      <c r="D1084" s="4" t="s">
+        <v>3718</v>
+      </c>
       <c r="E1084" s="3">
         <v>25</v>
       </c>
@@ -30223,7 +31118,9 @@
       <c r="C1085" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="D1085" s="4"/>
+      <c r="D1085" s="4" t="s">
+        <v>3719</v>
+      </c>
       <c r="E1085" s="3">
         <v>25</v>
       </c>
@@ -30244,7 +31141,9 @@
       <c r="C1086" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="D1086" s="4"/>
+      <c r="D1086" s="4" t="s">
+        <v>3720</v>
+      </c>
       <c r="E1086" s="3">
         <v>28</v>
       </c>
@@ -30265,7 +31164,9 @@
       <c r="C1087" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="D1087" s="4"/>
+      <c r="D1087" s="4" t="s">
+        <v>3721</v>
+      </c>
       <c r="E1087" s="3">
         <v>25</v>
       </c>
@@ -30286,7 +31187,9 @@
       <c r="C1088" s="2" t="s">
         <v>2162</v>
       </c>
-      <c r="D1088" s="4"/>
+      <c r="D1088" s="4" t="s">
+        <v>3722</v>
+      </c>
       <c r="E1088" s="3">
         <v>25</v>
       </c>
@@ -30622,7 +31525,9 @@
       <c r="C1110" s="2" t="s">
         <v>2230</v>
       </c>
-      <c r="D1110" s="4"/>
+      <c r="D1110" s="4" t="s">
+        <v>3723</v>
+      </c>
       <c r="E1110" s="3">
         <v>43</v>
       </c>
@@ -30763,7 +31668,9 @@
       <c r="C1119" s="2" t="s">
         <v>2268</v>
       </c>
-      <c r="D1119" s="4"/>
+      <c r="D1119" s="4" t="s">
+        <v>3724</v>
+      </c>
       <c r="E1119" s="3">
         <v>19</v>
       </c>
@@ -30781,7 +31688,9 @@
       <c r="B1120" s="2" t="s">
         <v>2272</v>
       </c>
-      <c r="C1120" s="2"/>
+      <c r="C1120" s="2" t="s">
+        <v>2268</v>
+      </c>
       <c r="D1120" s="4"/>
       <c r="E1120" s="3"/>
       <c r="F1120" s="3"/>
@@ -30794,7 +31703,9 @@
       <c r="B1121" s="2" t="s">
         <v>2274</v>
       </c>
-      <c r="C1121" s="2"/>
+      <c r="C1121" s="2" t="s">
+        <v>2268</v>
+      </c>
       <c r="D1121" s="4"/>
       <c r="E1121" s="3"/>
       <c r="F1121" s="3"/>
@@ -30807,7 +31718,9 @@
       <c r="B1122" s="2" t="s">
         <v>2276</v>
       </c>
-      <c r="C1122" s="2"/>
+      <c r="C1122" s="2" t="s">
+        <v>2268</v>
+      </c>
       <c r="D1122" s="4"/>
       <c r="E1122" s="3"/>
       <c r="F1122" s="3"/>
@@ -30823,7 +31736,9 @@
       <c r="C1123" s="2" t="s">
         <v>2268</v>
       </c>
-      <c r="D1123" s="4"/>
+      <c r="D1123" s="4" t="s">
+        <v>3725</v>
+      </c>
       <c r="E1123" s="3">
         <v>45</v>
       </c>
@@ -30844,7 +31759,9 @@
       <c r="C1124" s="2" t="s">
         <v>2268</v>
       </c>
-      <c r="D1124" s="4"/>
+      <c r="D1124" s="4" t="s">
+        <v>3726</v>
+      </c>
       <c r="E1124" s="3">
         <v>12</v>
       </c>
@@ -30880,7 +31797,9 @@
       <c r="C1126" s="2" t="s">
         <v>2285</v>
       </c>
-      <c r="D1126" s="4"/>
+      <c r="D1126" s="4" t="s">
+        <v>3727</v>
+      </c>
       <c r="E1126" s="3">
         <v>5</v>
       </c>
@@ -30901,7 +31820,9 @@
       <c r="C1127" s="2" t="s">
         <v>2285</v>
       </c>
-      <c r="D1127" s="4"/>
+      <c r="D1127" s="4" t="s">
+        <v>3728</v>
+      </c>
       <c r="E1127" s="3">
         <v>1</v>
       </c>
@@ -30937,7 +31858,9 @@
       <c r="C1129" s="2" t="s">
         <v>2285</v>
       </c>
-      <c r="D1129" s="4"/>
+      <c r="D1129" s="4" t="s">
+        <v>3729</v>
+      </c>
       <c r="E1129" s="3">
         <v>6</v>
       </c>
@@ -30958,7 +31881,9 @@
       <c r="C1130" s="2" t="s">
         <v>2285</v>
       </c>
-      <c r="D1130" s="4"/>
+      <c r="D1130" s="4" t="s">
+        <v>3730</v>
+      </c>
       <c r="E1130" s="3">
         <v>35</v>
       </c>
@@ -31009,7 +31934,9 @@
       <c r="C1133" s="2" t="s">
         <v>2301</v>
       </c>
-      <c r="D1133" s="4"/>
+      <c r="D1133" s="4" t="s">
+        <v>3731</v>
+      </c>
       <c r="E1133" s="3">
         <v>35</v>
       </c>
@@ -31030,7 +31957,9 @@
       <c r="C1134" s="2" t="s">
         <v>2304</v>
       </c>
-      <c r="D1134" s="4"/>
+      <c r="D1134" s="4" t="s">
+        <v>3732</v>
+      </c>
       <c r="E1134" s="3">
         <v>105</v>
       </c>
@@ -31051,7 +31980,9 @@
       <c r="C1135" s="2" t="s">
         <v>2304</v>
       </c>
-      <c r="D1135" s="4"/>
+      <c r="D1135" s="4" t="s">
+        <v>3733</v>
+      </c>
       <c r="E1135" s="3">
         <v>130</v>
       </c>
@@ -31072,7 +32003,9 @@
       <c r="C1136" s="2" t="s">
         <v>2304</v>
       </c>
-      <c r="D1136" s="4"/>
+      <c r="D1136" s="4" t="s">
+        <v>3734</v>
+      </c>
       <c r="E1136" s="3">
         <v>185</v>
       </c>
@@ -31391,7 +32324,9 @@
       <c r="C1157" s="2" t="s">
         <v>2354</v>
       </c>
-      <c r="D1157" s="4"/>
+      <c r="D1157" s="4" t="s">
+        <v>3735</v>
+      </c>
       <c r="E1157" s="3">
         <v>3</v>
       </c>
@@ -31412,7 +32347,9 @@
       <c r="C1158" s="2" t="s">
         <v>2354</v>
       </c>
-      <c r="D1158" s="4"/>
+      <c r="D1158" s="4" t="s">
+        <v>3736</v>
+      </c>
       <c r="E1158" s="3">
         <v>3</v>
       </c>
@@ -31448,7 +32385,9 @@
       <c r="C1160" s="2" t="s">
         <v>2354</v>
       </c>
-      <c r="D1160" s="4"/>
+      <c r="D1160" s="4" t="s">
+        <v>3737</v>
+      </c>
       <c r="E1160" s="3">
         <v>5</v>
       </c>
@@ -31469,7 +32408,9 @@
       <c r="C1161" s="2" t="s">
         <v>2354</v>
       </c>
-      <c r="D1161" s="4"/>
+      <c r="D1161" s="4" t="s">
+        <v>3739</v>
+      </c>
       <c r="E1161" s="3">
         <v>5</v>
       </c>
@@ -31700,7 +32641,9 @@
       <c r="C1176" s="2" t="s">
         <v>2387</v>
       </c>
-      <c r="D1176" s="4"/>
+      <c r="D1176" s="4" t="s">
+        <v>3738</v>
+      </c>
       <c r="E1176" s="3">
         <v>39</v>
       </c>
@@ -31796,7 +32739,9 @@
       <c r="C1182" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1182" s="4"/>
+      <c r="D1182" s="4" t="s">
+        <v>3740</v>
+      </c>
       <c r="E1182" s="3">
         <v>18</v>
       </c>
@@ -31817,7 +32762,9 @@
       <c r="C1183" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1183" s="4"/>
+      <c r="D1183" s="4" t="s">
+        <v>3741</v>
+      </c>
       <c r="E1183" s="3">
         <v>28</v>
       </c>
@@ -31838,7 +32785,9 @@
       <c r="C1184" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1184" s="4"/>
+      <c r="D1184" s="4" t="s">
+        <v>3742</v>
+      </c>
       <c r="E1184" s="3">
         <v>20</v>
       </c>
@@ -31889,7 +32838,9 @@
       <c r="C1187" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1187" s="4"/>
+      <c r="D1187" s="4" t="s">
+        <v>3743</v>
+      </c>
       <c r="E1187" s="3">
         <v>22</v>
       </c>
@@ -31970,7 +32921,9 @@
       <c r="C1192" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1192" s="4"/>
+      <c r="D1192" s="4" t="s">
+        <v>3744</v>
+      </c>
       <c r="E1192" s="3">
         <v>20</v>
       </c>
@@ -32051,7 +33004,9 @@
       <c r="C1197" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1197" s="4"/>
+      <c r="D1197" s="4" t="s">
+        <v>3745</v>
+      </c>
       <c r="E1197" s="3">
         <v>21</v>
       </c>
@@ -32072,7 +33027,9 @@
       <c r="C1198" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1198" s="4"/>
+      <c r="D1198" s="4" t="s">
+        <v>3746</v>
+      </c>
       <c r="E1198" s="3">
         <v>22</v>
       </c>
@@ -32093,7 +33050,9 @@
       <c r="C1199" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1199" s="4"/>
+      <c r="D1199" s="4" t="s">
+        <v>3747</v>
+      </c>
       <c r="E1199" s="3">
         <v>20</v>
       </c>
@@ -32414,7 +33373,9 @@
       <c r="C1220" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1220" s="4"/>
+      <c r="D1220" s="4" t="s">
+        <v>3748</v>
+      </c>
       <c r="E1220" s="3">
         <v>22</v>
       </c>
@@ -32435,7 +33396,9 @@
       <c r="C1221" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1221" s="4"/>
+      <c r="D1221" s="4" t="s">
+        <v>3749</v>
+      </c>
       <c r="E1221" s="3">
         <v>30</v>
       </c>
@@ -32456,7 +33419,9 @@
       <c r="C1222" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1222" s="4"/>
+      <c r="D1222" s="4" t="s">
+        <v>3750</v>
+      </c>
       <c r="E1222" s="3">
         <v>42</v>
       </c>
@@ -32473,7 +33438,9 @@
       <c r="C1223" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1223" s="4"/>
+      <c r="D1223" s="4" t="s">
+        <v>3751</v>
+      </c>
       <c r="E1223" s="3">
         <v>44</v>
       </c>
@@ -32494,10 +33461,18 @@
       <c r="C1224" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1224" s="4"/>
-      <c r="E1224" s="3"/>
-      <c r="F1224" s="3"/>
-      <c r="G1224" s="3"/>
+      <c r="D1224" s="4" t="s">
+        <v>3753</v>
+      </c>
+      <c r="E1224" s="3">
+        <v>28</v>
+      </c>
+      <c r="F1224" s="3">
+        <v>27</v>
+      </c>
+      <c r="G1224" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="1225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1225" s="2" t="s">
@@ -32509,7 +33484,9 @@
       <c r="C1225" s="2" t="s">
         <v>2410</v>
       </c>
-      <c r="D1225" s="4"/>
+      <c r="D1225" s="4" t="s">
+        <v>3752</v>
+      </c>
       <c r="E1225" s="3">
         <v>23</v>
       </c>
@@ -39881,11 +40858,15 @@
     <hyperlink ref="D441" r:id="rId7" xr:uid="{56C60A7B-22FE-4056-B279-2E1F623167B4}"/>
     <hyperlink ref="D593" r:id="rId8" xr:uid="{55D0DE41-071D-4884-AA9A-CBB36ADAF9D2}"/>
     <hyperlink ref="D592" r:id="rId9" xr:uid="{A5BC89BB-873D-44FC-8F0C-F479B62DAD2C}"/>
+    <hyperlink ref="D604" r:id="rId10" display="https://drive.google.com/file/d/1OM-wyc2bD71QOjvG9SkROq2OWov_cFb7/view?usp=drive_link" xr:uid="{22A44C61-13E7-4509-8A2D-7C647BC53C0A}"/>
+    <hyperlink ref="D613" r:id="rId11" display="https://drive.google.com/file/d/1Ieu9mxGIHuN6HEu48a8LGrFPaJijGB2j/view?usp=drive_link" xr:uid="{931B71D0-ADD9-42A6-ADA7-C281DCA38791}"/>
+    <hyperlink ref="D656" r:id="rId12" display="https://drive.google.com/file/d/1rHBmip5FiOCaG_gsNwbInGjugotrRFdE/view?usp=drive_link" xr:uid="{75263299-1E73-45E5-A302-11703911D42E}"/>
+    <hyperlink ref="D621" r:id="rId13" xr:uid="{37CC646C-9866-4150-8007-561F676CF959}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>